--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0B54557-4FF7-4000-BD65-0AA31D937DDC}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2327CCE0-9B4A-4D12-AD74-CC2DA4EBE3D9}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
@@ -598,53 +598,83 @@
       <c r="C14" s="2">
         <v>1.8985000000000001</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2">
+        <v>1.7608999999999999</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="B15">
+        <v>0.51</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1.8929</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1.7766</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1.88</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1.7897000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>0.59</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1.8823000000000001</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1.8021</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>0.622</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1.8936999999999999</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1.8011999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2327CCE0-9B4A-4D12-AD74-CC2DA4EBE3D9}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673256C3-1EDA-41B5-A018-B2604A70920E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
@@ -47,10 +47,10 @@
     <t>Distanza massa esterna (m)</t>
   </si>
   <si>
-    <t>T2 (massa interna) (s)</t>
+    <t>T2 (massa esterna) (s)</t>
   </si>
   <si>
-    <t>T1 (massa esterna) (s)</t>
+    <t>T1 (coltello 1) (s)</t>
   </si>
 </sst>
 </file>
@@ -438,8 +438,8 @@
   <cols>
     <col min="1" max="1" width="21.86328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -647,11 +647,23 @@
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="B19">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1.8996</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1.8382000000000001</v>
+      </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C20" s="2"/>
+      <c r="B20">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1.8989</v>
+      </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673256C3-1EDA-41B5-A018-B2604A70920E}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19B4BF02-B3B5-4E92-9B61-62E0336C9512}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
@@ -664,19 +664,42 @@
       <c r="C20" s="2">
         <v>1.8989</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" s="2">
+        <v>1.8492999999999999</v>
+      </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+      <c r="B21">
+        <v>0.74</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1.9069</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1.8694</v>
+      </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1.9159999999999999</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1.8993</v>
+      </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="B23">
+        <v>0.81</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1.9296</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1.9175</v>
+      </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C24" s="2"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19B4BF02-B3B5-4E92-9B61-62E0336C9512}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58AD79D5-3760-44E2-BBEE-DDDAD9E5FB96}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
@@ -702,12 +702,26 @@
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1.9403999999999999</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.9319</v>
+      </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="B25">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1.9753000000000001</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1.9626999999999999</v>
+      </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.45">
       <c r="C26" s="2"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58AD79D5-3760-44E2-BBEE-DDDAD9E5FB96}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EED9DE11-9A6E-42CE-8426-BF2414C80738}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
@@ -724,8 +724,15 @@
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="B26">
+        <v>0.92</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1.9931000000000001</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1.9933000000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EED9DE11-9A6E-42CE-8426-BF2414C80738}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{625FB48E-718D-4A74-B049-AF73D0F29CEC}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
   <si>
     <t>Distanza massa interna (m)</t>
   </si>
@@ -433,16 +433,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998A0AEA-104B-451D-928D-16D15628F08A}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.86328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.1328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.06640625" customWidth="1"/>
+    <col min="7" max="7" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -455,8 +459,17 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0.12</v>
       </c>
@@ -469,8 +482,17 @@
       <c r="D2" s="2">
         <v>1.9543999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="G2">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="H2">
+        <v>1.9802999999999999</v>
+      </c>
+      <c r="I2">
+        <v>1.9879</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B3">
         <v>0.1</v>
       </c>
@@ -481,7 +503,7 @@
         <v>1.9044000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B4">
         <v>0.13</v>
       </c>
@@ -492,7 +514,7 @@
         <v>1.8761000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B5">
         <v>0.16300000000000001</v>
       </c>
@@ -503,7 +525,7 @@
         <v>1.8714</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B6">
         <v>0.19</v>
       </c>
@@ -514,7 +536,7 @@
         <v>1.8234999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B7">
         <v>0.22</v>
       </c>
@@ -525,7 +547,7 @@
         <v>1.8037000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B8">
         <v>0.245</v>
       </c>
@@ -535,8 +557,17 @@
       <c r="D8" s="2">
         <v>1.76</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="G8">
+        <v>0.92</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1.9931000000000001</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1.9933000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B9">
         <v>0.27</v>
       </c>
@@ -547,7 +578,7 @@
         <v>1.7618</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B10">
         <v>0.30499999999999999</v>
       </c>
@@ -558,7 +589,7 @@
         <v>1.7654000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B11">
         <v>0.33700000000000002</v>
       </c>
@@ -569,7 +600,7 @@
         <v>1.7536</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B12">
         <v>0.379</v>
       </c>
@@ -580,7 +611,7 @@
         <v>1.7468999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B13">
         <v>0.42</v>
       </c>
@@ -591,7 +622,7 @@
         <v>1.7565999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B14">
         <v>0.46500000000000002</v>
       </c>
@@ -602,7 +633,7 @@
         <v>1.7608999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B15">
         <v>0.51</v>
       </c>
@@ -613,7 +644,7 @@
         <v>1.7766</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B16">
         <v>0.55500000000000005</v>
       </c>
@@ -721,17 +752,6 @@
       </c>
       <c r="D25" s="2">
         <v>1.9626999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B26">
-        <v>0.92</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1.9931000000000001</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1.9933000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{625FB48E-718D-4A74-B049-AF73D0F29CEC}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5033CF30-1C11-47FB-8A05-B5CE97F2AF0F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
+    <sheet name="Intersezione" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -433,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998A0AEA-104B-451D-928D-16D15628F08A}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.86328125" bestFit="1" customWidth="1"/>
@@ -446,7 +447,7 @@
     <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -459,17 +460,8 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0.12</v>
       </c>
@@ -482,17 +474,8 @@
       <c r="D2" s="2">
         <v>1.9543999999999999</v>
       </c>
-      <c r="G2">
-        <v>0.91500000000000004</v>
-      </c>
-      <c r="H2">
-        <v>1.9802999999999999</v>
-      </c>
-      <c r="I2">
-        <v>1.9879</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B3">
         <v>0.1</v>
       </c>
@@ -503,7 +486,7 @@
         <v>1.9044000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B4">
         <v>0.13</v>
       </c>
@@ -514,7 +497,7 @@
         <v>1.8761000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5">
         <v>0.16300000000000001</v>
       </c>
@@ -525,7 +508,7 @@
         <v>1.8714</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B6">
         <v>0.19</v>
       </c>
@@ -536,7 +519,7 @@
         <v>1.8234999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B7">
         <v>0.22</v>
       </c>
@@ -547,7 +530,7 @@
         <v>1.8037000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B8">
         <v>0.245</v>
       </c>
@@ -557,17 +540,8 @@
       <c r="D8" s="2">
         <v>1.76</v>
       </c>
-      <c r="G8">
-        <v>0.92</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1.9931000000000001</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1.9933000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B9">
         <v>0.27</v>
       </c>
@@ -578,7 +552,7 @@
         <v>1.7618</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B10">
         <v>0.30499999999999999</v>
       </c>
@@ -589,7 +563,7 @@
         <v>1.7654000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B11">
         <v>0.33700000000000002</v>
       </c>
@@ -600,7 +574,7 @@
         <v>1.7536</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12">
         <v>0.379</v>
       </c>
@@ -611,7 +585,7 @@
         <v>1.7468999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B13">
         <v>0.42</v>
       </c>
@@ -622,7 +596,7 @@
         <v>1.7565999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B14">
         <v>0.46500000000000002</v>
       </c>
@@ -633,7 +607,7 @@
         <v>1.7608999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B15">
         <v>0.51</v>
       </c>
@@ -644,7 +618,7 @@
         <v>1.7766</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B16">
         <v>0.55500000000000005</v>
       </c>
@@ -752,6 +726,76 @@
       </c>
       <c r="D25" s="2">
         <v>1.9626999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="C26">
+        <v>1.9802999999999999</v>
+      </c>
+      <c r="D26">
+        <v>1.9879</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B27">
+        <v>0.92</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1.9931000000000001</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1.9933000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2331EE30-F3F4-48C6-BC63-D4000596DD25}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="B2">
+        <v>1.9802999999999999</v>
+      </c>
+      <c r="C2">
+        <v>1.9879</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>0.92</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1.9931000000000001</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1.9933000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5033CF30-1C11-47FB-8A05-B5CE97F2AF0F}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4046DB2C-706E-4F93-8F90-7CFAF804AF0B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
     <sheet name="Intersezione" sheetId="2" r:id="rId2"/>
+    <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
   <si>
     <t>Distanza massa interna (m)</t>
   </si>
@@ -52,6 +53,24 @@
   </si>
   <si>
     <t>T1 (coltello 1) (s)</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Deviazione standard</t>
+  </si>
+  <si>
+    <t>Distanza (m)</t>
+  </si>
+  <si>
+    <t>h (m)</t>
+  </si>
+  <si>
+    <t>cateto opposto (m)</t>
+  </si>
+  <si>
+    <t>Errore sulla misura (m)</t>
   </si>
 </sst>
 </file>
@@ -70,7 +89,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -83,8 +102,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -92,14 +117,147 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -757,48 +915,316 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2331EE30-F3F4-48C6-BC63-D4000596DD25}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2">
+      <c r="D1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="17">
         <v>0.91500000000000004</v>
       </c>
-      <c r="B2">
-        <v>1.9802999999999999</v>
-      </c>
-      <c r="C2">
-        <v>1.9879</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8">
+      <c r="B2" s="9">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1.9834000000000001</v>
+      </c>
+      <c r="D2" s="17">
         <v>0.92</v>
       </c>
-      <c r="B8" s="2">
-        <v>1.9931000000000001</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1.9933000000000001</v>
-      </c>
+      <c r="E2" s="11">
+        <v>1.9897</v>
+      </c>
+      <c r="F2" s="10">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="G2">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="H2">
+        <v>0.09</v>
+      </c>
+      <c r="I2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="18"/>
+      <c r="B3" s="11">
+        <v>1.9903999999999999</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1.9888999999999999</v>
+      </c>
+      <c r="D3" s="18"/>
+      <c r="E3" s="11">
+        <v>1.9885999999999999</v>
+      </c>
+      <c r="F3" s="10">
+        <v>1.9921</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="18"/>
+      <c r="B4" s="11">
+        <v>1.9878</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1.9869000000000001</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="11">
+        <v>1.9895</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1.9892000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="18"/>
+      <c r="B5" s="11">
+        <v>1.9887999999999999</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1.9882</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="11">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1.9832000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="18"/>
+      <c r="B6" s="11">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1.9861</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="11">
+        <v>1.9835</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1.9914000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="18"/>
+      <c r="B7" s="11">
+        <v>1.9893000000000001</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1.99</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="11">
+        <v>1.9898</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1.9901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="18"/>
+      <c r="B8" s="11">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1.9866999999999999</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="11">
+        <v>1.99</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1.9899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="18"/>
+      <c r="B9" s="11">
+        <v>1.9869000000000001</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1.9855</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="11">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1.9891000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="18"/>
+      <c r="B10" s="11">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1.984</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="11">
+        <v>1.9898</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1.9921</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="18"/>
+      <c r="B11" s="11">
+        <v>1.9873000000000001</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1.9853000000000001</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="11">
+        <v>1.9903999999999999</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1.9881</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="12">
+        <f>AVERAGE(B2:B11)</f>
+        <v>1.9887500000000002</v>
+      </c>
+      <c r="C12" s="4">
+        <f>AVERAGE(C2:C11)</f>
+        <v>1.9864999999999999</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="14">
+        <f>AVERAGE(E2:E11)</f>
+        <v>1.9890900000000002</v>
+      </c>
+      <c r="F12" s="15">
+        <f>AVERAGE(F2:F11)</f>
+        <v>1.98963</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="13">
+        <f>_xlfn.STDEV.S(B2:B11)</f>
+        <v>1.1993053545003578E-3</v>
+      </c>
+      <c r="C13" s="6">
+        <f>_xlfn.STDEV.S(C2:C11)</f>
+        <v>2.0965580258021552E-3</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="13">
+        <f>_xlfn.STDEV.S(E2:E11)</f>
+        <v>2.0512597755200563E-3</v>
+      </c>
+      <c r="F13" s="6">
+        <f>_xlfn.STDEV.S(F2:F11)</f>
+        <v>2.6234201595118625E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCB5B1B-A29A-4C04-A627-A0C9CC08624F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4046DB2C-706E-4F93-8F90-7CFAF804AF0B}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E3735F5-EE2E-4226-91F9-1E3EDD97C4FE}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
     <sheet name="Intersezione" sheetId="2" r:id="rId2"/>
-    <sheet name="Foglio3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -109,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -145,6 +144,15 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -158,6 +166,15 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
       <bottom style="medium">
@@ -235,29 +252,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -609,13 +635,13 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -623,288 +649,288 @@
       <c r="A2">
         <v>0.12</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="12">
         <v>0.08</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="26">
         <v>1.9995000000000001</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="27">
         <v>1.9543999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B3">
+      <c r="B3" s="12">
         <v>0.1</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="26">
         <v>1.9843</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="27">
         <v>1.9044000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B4">
+      <c r="B4" s="12">
         <v>0.13</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="26">
         <v>1.9690000000000001</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="27">
         <v>1.8761000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B5">
+      <c r="B5" s="12">
         <v>0.16300000000000001</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="26">
         <v>1.9643999999999999</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="27">
         <v>1.8714</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B6">
+      <c r="B6" s="12">
         <v>0.19</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="26">
         <v>1.9528000000000001</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="27">
         <v>1.8234999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B7">
+      <c r="B7" s="12">
         <v>0.22</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="26">
         <v>1.9461999999999999</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="27">
         <v>1.8037000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B8">
+      <c r="B8" s="12">
         <v>0.245</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="26">
         <v>1.9360999999999999</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="27">
         <v>1.76</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B9">
+      <c r="B9" s="12">
         <v>0.27</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="26">
         <v>1.9354</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="27">
         <v>1.7618</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B10">
+      <c r="B10" s="12">
         <v>0.30499999999999999</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="26">
         <v>1.921</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="27">
         <v>1.7654000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B11">
+      <c r="B11" s="12">
         <v>0.33700000000000002</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="26">
         <v>1.9114</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="27">
         <v>1.7536</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B12">
+      <c r="B12" s="12">
         <v>0.379</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="26">
         <v>1.903</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="27">
         <v>1.7468999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B13">
+      <c r="B13" s="12">
         <v>0.42</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="26">
         <v>1.9016</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="27">
         <v>1.7565999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B14">
+      <c r="B14" s="12">
         <v>0.46500000000000002</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="26">
         <v>1.8985000000000001</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="27">
         <v>1.7608999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B15">
+      <c r="B15" s="12">
         <v>0.51</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="26">
         <v>1.8929</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="27">
         <v>1.7766</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B16">
+      <c r="B16" s="12">
         <v>0.55500000000000005</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="26">
         <v>1.88</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="27">
         <v>1.7897000000000001</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B17">
+      <c r="B17" s="12">
         <v>0.59</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="26">
         <v>1.8823000000000001</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="27">
         <v>1.8021</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B18">
+      <c r="B18" s="12">
         <v>0.622</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="26">
         <v>1.8936999999999999</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="27">
         <v>1.8011999999999999</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19">
+      <c r="B19" s="12">
         <v>0.66300000000000003</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="26">
         <v>1.8996</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="27">
         <v>1.8382000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20">
+      <c r="B20" s="12">
         <v>0.70499999999999996</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="26">
         <v>1.8989</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="27">
         <v>1.8492999999999999</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B21">
+      <c r="B21" s="12">
         <v>0.74</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="26">
         <v>1.9069</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="27">
         <v>1.8694</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B22">
+      <c r="B22" s="12">
         <v>0.77500000000000002</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="26">
         <v>1.9159999999999999</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="27">
         <v>1.8993</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B23">
+      <c r="B23" s="12">
         <v>0.81</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="26">
         <v>1.9296</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="27">
         <v>1.9175</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B24">
+      <c r="B24" s="12">
         <v>0.83799999999999997</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="26">
         <v>1.9403999999999999</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="27">
         <v>1.9319</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B25">
+      <c r="B25" s="12">
         <v>0.88200000000000001</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="26">
         <v>1.9753000000000001</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="27">
         <v>1.9626999999999999</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B26">
+      <c r="B26" s="12">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="28">
         <v>1.9802999999999999</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="11">
         <v>1.9879</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B27">
+    <row r="27" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B27" s="14">
         <v>0.92</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="29">
         <v>1.9931000000000001</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="30">
         <v>1.9933000000000001</v>
       </c>
     </row>
@@ -930,212 +956,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="17">
+    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="18">
         <v>0.91500000000000004</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>1.9890000000000001</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="11">
         <v>1.9834000000000001</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="18">
         <v>0.92</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="12">
         <v>1.9897</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="11">
         <v>1.9911000000000001</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="14">
         <v>1.0049999999999999</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="6">
         <v>0.09</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="7">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="18"/>
-      <c r="B3" s="11">
+      <c r="A3" s="19"/>
+      <c r="B3" s="12">
         <v>1.9903999999999999</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="11">
         <v>1.9888999999999999</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="11">
+      <c r="D3" s="19"/>
+      <c r="E3" s="12">
         <v>1.9885999999999999</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="11">
         <v>1.9921</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="18"/>
-      <c r="B4" s="11">
+      <c r="A4" s="19"/>
+      <c r="B4" s="12">
         <v>1.9878</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="11">
         <v>1.9869000000000001</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="11">
+      <c r="D4" s="19"/>
+      <c r="E4" s="12">
         <v>1.9895</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="11">
         <v>1.9892000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="18"/>
-      <c r="B5" s="11">
+      <c r="A5" s="19"/>
+      <c r="B5" s="12">
         <v>1.9887999999999999</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="11">
         <v>1.9882</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="11">
+      <c r="D5" s="19"/>
+      <c r="E5" s="12">
         <v>1.9890000000000001</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="11">
         <v>1.9832000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="18"/>
-      <c r="B6" s="11">
+      <c r="A6" s="19"/>
+      <c r="B6" s="12">
         <v>1.9905999999999999</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="11">
         <v>1.9861</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="11">
+      <c r="D6" s="19"/>
+      <c r="E6" s="12">
         <v>1.9835</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <v>1.9914000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="18"/>
-      <c r="B7" s="11">
+      <c r="A7" s="19"/>
+      <c r="B7" s="12">
         <v>1.9893000000000001</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="11">
         <v>1.99</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="11">
+      <c r="D7" s="19"/>
+      <c r="E7" s="12">
         <v>1.9898</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <v>1.9901</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="18"/>
-      <c r="B8" s="11">
+      <c r="A8" s="19"/>
+      <c r="B8" s="12">
         <v>1.9886999999999999</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <v>1.9866999999999999</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="11">
+      <c r="D8" s="19"/>
+      <c r="E8" s="12">
         <v>1.99</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>1.9899</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="18"/>
-      <c r="B9" s="11">
+      <c r="A9" s="19"/>
+      <c r="B9" s="12">
         <v>1.9869000000000001</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <v>1.9855</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="11">
+      <c r="D9" s="19"/>
+      <c r="E9" s="12">
         <v>1.9905999999999999</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>1.9891000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="18"/>
-      <c r="B10" s="11">
+      <c r="A10" s="19"/>
+      <c r="B10" s="12">
         <v>1.9886999999999999</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <v>1.984</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="11">
+      <c r="D10" s="19"/>
+      <c r="E10" s="12">
         <v>1.9898</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="11">
         <v>1.9921</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="18"/>
-      <c r="B11" s="11">
+      <c r="A11" s="19"/>
+      <c r="B11" s="12">
         <v>1.9873000000000001</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="11">
         <v>1.9853000000000001</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="11">
+      <c r="D11" s="19"/>
+      <c r="E11" s="12">
         <v>1.9903999999999999</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>1.9881</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <f>AVERAGE(B2:B11)</f>
         <v>1.9887500000000002</v>
       </c>
@@ -1143,88 +1169,79 @@
         <f>AVERAGE(C2:C11)</f>
         <v>1.9864999999999999</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="15">
         <f>AVERAGE(E2:E11)</f>
         <v>1.9890900000000002</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="16">
         <f>AVERAGE(F2:F11)</f>
         <v>1.98963</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="14">
         <f>_xlfn.STDEV.S(B2:B11)</f>
         <v>1.1993053545003578E-3</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <f>_xlfn.STDEV.S(C2:C11)</f>
         <v>2.0965580258021552E-3</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="14">
         <f>_xlfn.STDEV.S(E2:E11)</f>
         <v>2.0512597755200563E-3</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <f>_xlfn.STDEV.S(F2:F11)</f>
         <v>2.6234201595118625E-3</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="D14" s="3"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="D15" s="3"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="D16" s="3"/>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D17" s="3"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D18" s="3"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D19" s="3"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D20" s="3"/>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D21" s="3"/>
+      <c r="D21" s="2"/>
     </row>
     <row r="22" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D22" s="3"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D23" s="3"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D24" s="3"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D25" s="3"/>
+      <c r="D25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCB5B1B-A29A-4C04-A627-A0C9CC08624F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E3735F5-EE2E-4226-91F9-1E3EDD97C4FE}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3663F103-B98B-4ECA-B978-6A1E1D7266C3}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
     <sheet name="Intersezione" sheetId="2" r:id="rId2"/>
+    <sheet name="Foglio1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
   <si>
     <t>Distanza massa interna (m)</t>
   </si>
@@ -77,7 +78,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -252,10 +253,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
@@ -263,13 +263,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -279,11 +279,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -635,13 +634,13 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
     </row>
@@ -649,288 +648,288 @@
       <c r="A2">
         <v>0.12</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>0.08</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="25">
         <v>1.9995000000000001</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="26">
         <v>1.9543999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>0.1</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="25">
         <v>1.9843</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="26">
         <v>1.9044000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>0.13</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="25">
         <v>1.9690000000000001</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="26">
         <v>1.8761000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>0.16300000000000001</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <v>1.9643999999999999</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="26">
         <v>1.8714</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>0.19</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>1.9528000000000001</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <v>1.8234999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>0.22</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
         <v>1.9461999999999999</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="26">
         <v>1.8037000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>0.245</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="25">
         <v>1.9360999999999999</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <v>1.76</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>0.27</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>1.9354</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="26">
         <v>1.7618</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>0.30499999999999999</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>1.921</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <v>1.7654000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0.33700000000000002</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="25">
         <v>1.9114</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="26">
         <v>1.7536</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>0.379</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <v>1.903</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="26">
         <v>1.7468999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>0.42</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="25">
         <v>1.9016</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="26">
         <v>1.7565999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>0.46500000000000002</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>1.8985000000000001</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="26">
         <v>1.7608999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>0.51</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="25">
         <v>1.8929</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="26">
         <v>1.7766</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>0.55500000000000005</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>1.88</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="26">
         <v>1.7897000000000001</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>0.59</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="25">
         <v>1.8823000000000001</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="26">
         <v>1.8021</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>0.622</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="25">
         <v>1.8936999999999999</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <v>1.8011999999999999</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>0.66300000000000003</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="25">
         <v>1.8996</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="26">
         <v>1.8382000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>0.70499999999999996</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="25">
         <v>1.8989</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="26">
         <v>1.8492999999999999</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>0.74</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <v>1.9069</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="26">
         <v>1.8694</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <v>0.77500000000000002</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="25">
         <v>1.9159999999999999</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="26">
         <v>1.8993</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <v>0.81</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="25">
         <v>1.9296</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="26">
         <v>1.9175</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>0.83799999999999997</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="25">
         <v>1.9403999999999999</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="26">
         <v>1.9319</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>0.88200000000000001</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="25">
         <v>1.9753000000000001</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="26">
         <v>1.9626999999999999</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26">
         <v>1.9802999999999999</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <v>1.9879</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="14">
+      <c r="B27" s="13">
         <v>0.92</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="27">
         <v>1.9931000000000001</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="28">
         <v>1.9933000000000001</v>
       </c>
     </row>
@@ -941,7 +940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2331EE30-F3F4-48C6-BC63-D4000596DD25}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
@@ -956,290 +955,525 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="18">
+      <c r="A2" s="17">
         <v>0.91500000000000004</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>1.9890000000000001</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>1.9834000000000001</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="17">
         <v>0.92</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <v>1.9897</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>1.9911000000000001</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="13">
         <v>1.0049999999999999</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>0.09</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="19"/>
-      <c r="B3" s="12">
+      <c r="A3" s="18"/>
+      <c r="B3" s="11">
         <v>1.9903999999999999</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>1.9888999999999999</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="12">
+      <c r="D3" s="18"/>
+      <c r="E3" s="11">
         <v>1.9885999999999999</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>1.9921</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="19"/>
-      <c r="B4" s="12">
+      <c r="A4" s="18"/>
+      <c r="B4" s="11">
         <v>1.9878</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>1.9869000000000001</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="12">
+      <c r="D4" s="18"/>
+      <c r="E4" s="11">
         <v>1.9895</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>1.9892000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="19"/>
-      <c r="B5" s="12">
+      <c r="A5" s="18"/>
+      <c r="B5" s="11">
         <v>1.9887999999999999</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>1.9882</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="12">
+      <c r="D5" s="18"/>
+      <c r="E5" s="11">
         <v>1.9890000000000001</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>1.9832000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="19"/>
-      <c r="B6" s="12">
+      <c r="A6" s="18"/>
+      <c r="B6" s="11">
         <v>1.9905999999999999</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>1.9861</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="12">
+      <c r="D6" s="18"/>
+      <c r="E6" s="11">
         <v>1.9835</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>1.9914000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="19"/>
-      <c r="B7" s="12">
+      <c r="A7" s="18"/>
+      <c r="B7" s="11">
         <v>1.9893000000000001</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>1.99</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="12">
+      <c r="D7" s="18"/>
+      <c r="E7" s="11">
         <v>1.9898</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>1.9901</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="19"/>
-      <c r="B8" s="12">
+      <c r="A8" s="18"/>
+      <c r="B8" s="11">
         <v>1.9886999999999999</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>1.9866999999999999</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="12">
+      <c r="D8" s="18"/>
+      <c r="E8" s="11">
         <v>1.99</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <v>1.9899</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="19"/>
-      <c r="B9" s="12">
+      <c r="A9" s="18"/>
+      <c r="B9" s="11">
         <v>1.9869000000000001</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>1.9855</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="12">
+      <c r="D9" s="18"/>
+      <c r="E9" s="11">
         <v>1.9905999999999999</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>1.9891000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="19"/>
-      <c r="B10" s="12">
+      <c r="A10" s="18"/>
+      <c r="B10" s="11">
         <v>1.9886999999999999</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <v>1.984</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="12">
+      <c r="D10" s="18"/>
+      <c r="E10" s="11">
         <v>1.9898</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>1.9921</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="19"/>
-      <c r="B11" s="12">
+      <c r="A11" s="18"/>
+      <c r="B11" s="11">
         <v>1.9873000000000001</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>1.9853000000000001</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="12">
+      <c r="D11" s="18"/>
+      <c r="E11" s="11">
         <v>1.9903999999999999</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <v>1.9881</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <f>AVERAGE(B2:B11)</f>
         <v>1.9887500000000002</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <f>AVERAGE(C2:C11)</f>
         <v>1.9864999999999999</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <f>AVERAGE(E2:E11)</f>
         <v>1.9890900000000002</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <f>AVERAGE(F2:F11)</f>
         <v>1.98963</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <f>_xlfn.STDEV.S(B2:B11)</f>
         <v>1.1993053545003578E-3</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <f>_xlfn.STDEV.S(C2:C11)</f>
         <v>2.0965580258021552E-3</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <f>_xlfn.STDEV.S(E2:E11)</f>
         <v>2.0512597755200563E-3</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <f>_xlfn.STDEV.S(F2:F11)</f>
         <v>2.6234201595118625E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.45">
-      <c r="D25" s="2"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A3B4CE-F596-452E-9DD8-1E4854DB4C41}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.46484375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="17">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="B2" s="9">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1.9834000000000001</v>
+      </c>
+      <c r="D2" s="17">
+        <v>0.92</v>
+      </c>
+      <c r="E2" s="11">
+        <v>1.9897</v>
+      </c>
+      <c r="F2" s="10">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="G2" s="13">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="I2" s="6">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="18"/>
+      <c r="B3" s="11">
+        <v>1.9903999999999999</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1.9888999999999999</v>
+      </c>
+      <c r="D3" s="18"/>
+      <c r="E3" s="11">
+        <v>1.9885999999999999</v>
+      </c>
+      <c r="F3" s="10">
+        <v>1.9921</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="18"/>
+      <c r="B4" s="11">
+        <v>1.9878</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1.9869000000000001</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="11">
+        <v>1.9895</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1.9892000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="18"/>
+      <c r="B5" s="11">
+        <v>1.9887999999999999</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1.9882</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="11">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1.9832000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="18"/>
+      <c r="B6" s="11">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1.9861</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="11">
+        <v>1.9835</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1.9914000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="18"/>
+      <c r="B7" s="11">
+        <v>1.9893000000000001</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1.99</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="11">
+        <v>1.9898</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1.9901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="18"/>
+      <c r="B8" s="11">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1.9866999999999999</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="11">
+        <v>1.99</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1.9899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="18"/>
+      <c r="B9" s="11">
+        <v>1.9869000000000001</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1.9855</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="11">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1.9891000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="18"/>
+      <c r="B10" s="11">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1.984</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="11">
+        <v>1.9898</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1.9921</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="18"/>
+      <c r="B11" s="11">
+        <v>1.9873000000000001</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1.9853000000000001</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="11">
+        <v>1.9903999999999999</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1.9881</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="12">
+        <f>AVERAGE(B2:B11)</f>
+        <v>1.9887500000000002</v>
+      </c>
+      <c r="C12" s="3">
+        <f>AVERAGE(C2:C11)</f>
+        <v>1.9864999999999999</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="14">
+        <f>AVERAGE(E2:E11)</f>
+        <v>1.9890900000000002</v>
+      </c>
+      <c r="F12" s="15">
+        <f>AVERAGE(F2:F11)</f>
+        <v>1.98963</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="13">
+        <f>_xlfn.STDEV.S(B2:B11)</f>
+        <v>1.1993053545003578E-3</v>
+      </c>
+      <c r="C13" s="6">
+        <f>_xlfn.STDEV.S(C2:C11)</f>
+        <v>2.0965580258021552E-3</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="13">
+        <f>_xlfn.STDEV.S(E2:E11)</f>
+        <v>2.0512597755200563E-3</v>
+      </c>
+      <c r="F13" s="6">
+        <f>_xlfn.STDEV.S(F2:F11)</f>
+        <v>2.6234201595118625E-3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="215" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3663F103-B98B-4ECA-B978-6A1E1D7266C3}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF5003AD-A6AF-4FDF-8EA1-90A9651AE19D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
   <si>
     <t>Distanza massa interna (m)</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Errore sulla misura (m)</t>
+  </si>
+  <si>
+    <t>Errore standard della media</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A3B4CE-F596-452E-9DD8-1E4854DB4C41}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
@@ -1475,6 +1478,19 @@
         <v>2.6234201595118625E-3</v>
       </c>
     </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <f>B13/SQRT(10)</f>
+        <v>3.7925365302567999E-4</v>
+      </c>
+      <c r="C14">
+        <f>C13/SQRT(10)</f>
+        <v>6.6298986082408758E-4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF5003AD-A6AF-4FDF-8EA1-90A9651AE19D}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{532E1217-C609-4F2B-9A0C-998A2213A34E}"/>
   <bookViews>
     <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
   <si>
     <t>Distanza massa interna (m)</t>
   </si>
@@ -1490,6 +1490,17 @@
         <f>C13/SQRT(10)</f>
         <v>6.6298986082408758E-4</v>
       </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <f>E13/SQRT(10)</f>
+        <v>6.4866529633290785E-4</v>
+      </c>
+      <c r="F14">
+        <f>F13/SQRT(10)</f>
+        <v>8.2959829636597285E-4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{532E1217-C609-4F2B-9A0C-998A2213A34E}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C502C29-A804-4BA8-B718-C7AD7104DBF7}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -1,16 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C502C29-A804-4BA8-B718-C7AD7104DBF7}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
@@ -18,77 +11,57 @@
     <sheet name="Foglio1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>Distanza massa interna (m)</t>
+    <t xml:space="preserve">Distanza massa interna (m)</t>
   </si>
   <si>
-    <t>Distanza massa esterna (m)</t>
+    <t xml:space="preserve">Distanza massa esterna (m)</t>
   </si>
   <si>
-    <t>T2 (massa esterna) (s)</t>
+    <t xml:space="preserve">T2 (massa esterna) (s)</t>
   </si>
   <si>
-    <t>T1 (coltello 1) (s)</t>
+    <t xml:space="preserve">T1 (coltello 1) (s)</t>
   </si>
   <si>
     <t>Media</t>
   </si>
   <si>
-    <t>Deviazione standard</t>
+    <t xml:space="preserve">Deviazione standard</t>
   </si>
   <si>
-    <t>Distanza (m)</t>
+    <t xml:space="preserve">Distanza (m)</t>
   </si>
   <si>
-    <t>h (m)</t>
+    <t xml:space="preserve">h (m)</t>
   </si>
   <si>
-    <t>cateto opposto (m)</t>
+    <t xml:space="preserve">cateto opposto (m)</t>
   </si>
   <si>
-    <t>Errore sulla misura (m)</t>
+    <t xml:space="preserve">Errore sulla misura (m)</t>
   </si>
   <si>
-    <t>Errore standard della media</t>
+    <t xml:space="preserve">Errore standard della media</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -101,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor indexed="5"/>
+        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
+        <bgColor/>
       </patternFill>
     </fill>
   </fills>
@@ -122,26 +95,26 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color/>
       </left>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color/>
       </top>
       <bottom/>
       <diagonal/>
@@ -150,7 +123,7 @@
       <left/>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color/>
       </top>
       <bottom/>
       <diagonal/>
@@ -158,22 +131,22 @@
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color/>
       </left>
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color/>
       </bottom>
       <diagonal/>
     </border>
@@ -182,24 +155,24 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color/>
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color/>
       </left>
       <right/>
       <top/>
@@ -209,7 +182,7 @@
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color/>
       </right>
       <top/>
       <bottom/>
@@ -217,23 +190,23 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color/>
       </right>
       <top/>
       <bottom/>
@@ -241,51 +214,51 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color/>
       </right>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -303,8 +276,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -347,8 +603,8 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
@@ -399,8 +655,8 @@
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
         <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
@@ -609,31 +865,24 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998A0AEA-104B-451D-928D-16D15628F08A}">
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.06640625" customWidth="1"/>
-    <col min="7" max="7" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="21.86328125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="22.1328125"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="13.796875"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="18"/>
+    <col customWidth="1" min="6" max="6" width="9.06640625"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="22.1328125"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="13.796875"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -647,12 +896,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2">
       <c r="A2">
         <v>0.12</v>
       </c>
       <c r="B2" s="11">
-        <v>0.08</v>
+        <v>8.0000000000000002e-002</v>
       </c>
       <c r="C2" s="25">
         <v>1.9995000000000001</v>
@@ -661,9 +910,9 @@
         <v>1.9543999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3">
       <c r="B3" s="11">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="C3" s="25">
         <v>1.9843</v>
@@ -672,7 +921,7 @@
         <v>1.9044000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4">
       <c r="B4" s="11">
         <v>0.13</v>
       </c>
@@ -683,7 +932,7 @@
         <v>1.8761000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5">
       <c r="B5" s="11">
         <v>0.16300000000000001</v>
       </c>
@@ -694,7 +943,7 @@
         <v>1.8714</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6">
       <c r="B6" s="11">
         <v>0.19</v>
       </c>
@@ -705,7 +954,7 @@
         <v>1.8234999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7">
       <c r="B7" s="11">
         <v>0.22</v>
       </c>
@@ -716,7 +965,7 @@
         <v>1.8037000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8">
       <c r="B8" s="11">
         <v>0.245</v>
       </c>
@@ -727,9 +976,9 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9">
       <c r="B9" s="11">
-        <v>0.27</v>
+        <v>0.27000000000000002</v>
       </c>
       <c r="C9" s="25">
         <v>1.9354</v>
@@ -738,7 +987,7 @@
         <v>1.7618</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10">
       <c r="B10" s="11">
         <v>0.30499999999999999</v>
       </c>
@@ -749,7 +998,7 @@
         <v>1.7654000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11">
       <c r="B11" s="11">
         <v>0.33700000000000002</v>
       </c>
@@ -760,7 +1009,7 @@
         <v>1.7536</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12">
       <c r="B12" s="11">
         <v>0.379</v>
       </c>
@@ -771,9 +1020,9 @@
         <v>1.7468999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13">
       <c r="B13" s="11">
-        <v>0.42</v>
+        <v>0.41999999999999998</v>
       </c>
       <c r="C13" s="25">
         <v>1.9016</v>
@@ -782,7 +1031,7 @@
         <v>1.7565999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14">
       <c r="B14" s="11">
         <v>0.46500000000000002</v>
       </c>
@@ -793,9 +1042,9 @@
         <v>1.7608999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15">
       <c r="B15" s="11">
-        <v>0.51</v>
+        <v>0.51000000000000001</v>
       </c>
       <c r="C15" s="25">
         <v>1.8929</v>
@@ -804,20 +1053,20 @@
         <v>1.7766</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16">
       <c r="B16" s="11">
         <v>0.55500000000000005</v>
       </c>
       <c r="C16" s="25">
-        <v>1.88</v>
+        <v>1.8799999999999999</v>
       </c>
       <c r="D16" s="26">
         <v>1.7897000000000001</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="17">
       <c r="B17" s="11">
-        <v>0.59</v>
+        <v>0.58999999999999997</v>
       </c>
       <c r="C17" s="25">
         <v>1.8823000000000001</v>
@@ -826,7 +1075,7 @@
         <v>1.8021</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="18">
       <c r="B18" s="11">
         <v>0.622</v>
       </c>
@@ -837,7 +1086,7 @@
         <v>1.8011999999999999</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="19">
       <c r="B19" s="11">
         <v>0.66300000000000003</v>
       </c>
@@ -848,7 +1097,7 @@
         <v>1.8382000000000001</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="20">
       <c r="B20" s="11">
         <v>0.70499999999999996</v>
       </c>
@@ -859,9 +1108,9 @@
         <v>1.8492999999999999</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="21">
       <c r="B21" s="11">
-        <v>0.74</v>
+        <v>0.73999999999999999</v>
       </c>
       <c r="C21" s="25">
         <v>1.9069</v>
@@ -870,7 +1119,7 @@
         <v>1.8694</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="22">
       <c r="B22" s="11">
         <v>0.77500000000000002</v>
       </c>
@@ -881,9 +1130,9 @@
         <v>1.8993</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="23">
       <c r="B23" s="11">
-        <v>0.81</v>
+        <v>0.81000000000000005</v>
       </c>
       <c r="C23" s="25">
         <v>1.9296</v>
@@ -892,7 +1141,7 @@
         <v>1.9175</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="24">
       <c r="B24" s="11">
         <v>0.83799999999999997</v>
       </c>
@@ -903,7 +1152,7 @@
         <v>1.9319</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="25">
       <c r="B25" s="11">
         <v>0.88200000000000001</v>
       </c>
@@ -914,7 +1163,7 @@
         <v>1.9626999999999999</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="26">
       <c r="B26" s="11">
         <v>0.91500000000000004</v>
       </c>
@@ -925,9 +1174,9 @@
         <v>1.9879</v>
       </c>
     </row>
-    <row r="27" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" ht="14.65">
       <c r="B27" s="13">
-        <v>0.92</v>
+        <v>0.92000000000000004</v>
       </c>
       <c r="C27" s="27">
         <v>1.9931000000000001</v>
@@ -937,27 +1186,26 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2331EE30-F3F4-48C6-BC63-D4000596DD25}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.46484375" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="22.1328125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="15.6640625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="18.46484375"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="16.59765625"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="13.796875"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="18"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="5.73046875"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="15.6640625"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="18.46484375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -986,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" ht="14.65">
       <c r="A2" s="17">
         <v>0.91500000000000004</v>
       </c>
@@ -997,7 +1245,7 @@
         <v>1.9834000000000001</v>
       </c>
       <c r="D2" s="17">
-        <v>0.92</v>
+        <v>0.92000000000000004</v>
       </c>
       <c r="E2" s="11">
         <v>1.9897</v>
@@ -1009,13 +1257,13 @@
         <v>1.0049999999999999</v>
       </c>
       <c r="H2" s="5">
-        <v>0.09</v>
+        <v>8.9999999999999997e-002</v>
       </c>
       <c r="I2" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="18"/>
       <c r="B3" s="11">
         <v>1.9903999999999999</v>
@@ -1031,7 +1279,7 @@
         <v>1.9921</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4">
       <c r="A4" s="18"/>
       <c r="B4" s="11">
         <v>1.9878</v>
@@ -1047,7 +1295,7 @@
         <v>1.9892000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5">
       <c r="A5" s="18"/>
       <c r="B5" s="11">
         <v>1.9887999999999999</v>
@@ -1063,7 +1311,7 @@
         <v>1.9832000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6">
       <c r="A6" s="18"/>
       <c r="B6" s="11">
         <v>1.9905999999999999</v>
@@ -1079,7 +1327,7 @@
         <v>1.9914000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7">
       <c r="A7" s="18"/>
       <c r="B7" s="11">
         <v>1.9893000000000001</v>
@@ -1095,7 +1343,7 @@
         <v>1.9901</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8">
       <c r="A8" s="18"/>
       <c r="B8" s="11">
         <v>1.9886999999999999</v>
@@ -1111,7 +1359,7 @@
         <v>1.9899</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9">
       <c r="A9" s="18"/>
       <c r="B9" s="11">
         <v>1.9869000000000001</v>
@@ -1127,7 +1375,7 @@
         <v>1.9891000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10">
       <c r="A10" s="18"/>
       <c r="B10" s="11">
         <v>1.9886999999999999</v>
@@ -1143,7 +1391,7 @@
         <v>1.9921</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" ht="14.65">
       <c r="A11" s="18"/>
       <c r="B11" s="11">
         <v>1.9873000000000001</v>
@@ -1159,7 +1407,7 @@
         <v>1.9881</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" ht="14.65">
       <c r="A12" s="20" t="s">
         <v>4</v>
       </c>
@@ -1183,52 +1431,51 @@
         <v>1.98963</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" ht="14.65">
       <c r="A13" s="21" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="13">
         <f>_xlfn.STDEV.S(B2:B11)</f>
-        <v>1.1993053545003578E-3</v>
+        <v>1.1993053545003578e-003</v>
       </c>
       <c r="C13" s="6">
         <f>_xlfn.STDEV.S(C2:C11)</f>
-        <v>2.0965580258021552E-3</v>
+        <v>2.0965580258021552e-003</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="13">
         <f>_xlfn.STDEV.S(E2:E11)</f>
-        <v>2.0512597755200563E-3</v>
+        <v>2.0512597755200563e-003</v>
       </c>
       <c r="F13" s="6">
         <f>_xlfn.STDEV.S(F2:F11)</f>
-        <v>2.6234201595118625E-3</v>
+        <v>2.6234201595118625e-003</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A3B4CE-F596-452E-9DD8-1E4854DB4C41}">
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.46484375" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="22.1328125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="13.796875"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="18"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="16.59765625"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="13.796875"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="18"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="5.73046875"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="15.6640625"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="18.46484375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" ht="14.65">
       <c r="A2" s="17">
         <v>0.91500000000000004</v>
       </c>
@@ -1268,7 +1515,7 @@
         <v>1.9834000000000001</v>
       </c>
       <c r="D2" s="17">
-        <v>0.92</v>
+        <v>0.92000000000000004</v>
       </c>
       <c r="E2" s="11">
         <v>1.9897</v>
@@ -1280,13 +1527,13 @@
         <v>1.0049999999999999</v>
       </c>
       <c r="H2" s="5">
-        <v>0.09</v>
+        <v>8.9999999999999997e-002</v>
       </c>
       <c r="I2" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="18"/>
       <c r="B3" s="11">
         <v>1.9903999999999999</v>
@@ -1302,7 +1549,7 @@
         <v>1.9921</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4">
       <c r="A4" s="18"/>
       <c r="B4" s="11">
         <v>1.9878</v>
@@ -1318,7 +1565,7 @@
         <v>1.9892000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5">
       <c r="A5" s="18"/>
       <c r="B5" s="11">
         <v>1.9887999999999999</v>
@@ -1334,7 +1581,7 @@
         <v>1.9832000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6">
       <c r="A6" s="18"/>
       <c r="B6" s="11">
         <v>1.9905999999999999</v>
@@ -1350,7 +1597,7 @@
         <v>1.9914000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7">
       <c r="A7" s="18"/>
       <c r="B7" s="11">
         <v>1.9893000000000001</v>
@@ -1366,7 +1613,7 @@
         <v>1.9901</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8">
       <c r="A8" s="18"/>
       <c r="B8" s="11">
         <v>1.9886999999999999</v>
@@ -1382,7 +1629,7 @@
         <v>1.9899</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9">
       <c r="A9" s="18"/>
       <c r="B9" s="11">
         <v>1.9869000000000001</v>
@@ -1398,7 +1645,7 @@
         <v>1.9891000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10">
       <c r="A10" s="18"/>
       <c r="B10" s="11">
         <v>1.9886999999999999</v>
@@ -1414,7 +1661,7 @@
         <v>1.9921</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" ht="14.65">
       <c r="A11" s="18"/>
       <c r="B11" s="11">
         <v>1.9873000000000001</v>
@@ -1430,7 +1677,7 @@
         <v>1.9881</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" ht="14.65">
       <c r="A12" s="20" t="s">
         <v>4</v>
       </c>
@@ -1454,55 +1701,55 @@
         <v>1.98963</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" ht="14.65">
       <c r="A13" s="21" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="13">
         <f>_xlfn.STDEV.S(B2:B11)</f>
-        <v>1.1993053545003578E-3</v>
+        <v>1.1993053545003578e-003</v>
       </c>
       <c r="C13" s="6">
         <f>_xlfn.STDEV.S(C2:C11)</f>
-        <v>2.0965580258021552E-3</v>
+        <v>2.0965580258021552e-003</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E13" s="13">
         <f>_xlfn.STDEV.S(E2:E11)</f>
-        <v>2.0512597755200563E-3</v>
+        <v>2.0512597755200563e-003</v>
       </c>
       <c r="F13" s="6">
         <f>_xlfn.STDEV.S(F2:F11)</f>
-        <v>2.6234201595118625E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+        <v>2.6234201595118625e-003</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>10</v>
       </c>
       <c r="B14">
         <f>B13/SQRT(10)</f>
-        <v>3.7925365302567999E-4</v>
+        <v>3.7925365302567999e-004</v>
       </c>
       <c r="C14">
         <f>C13/SQRT(10)</f>
-        <v>6.6298986082408758E-4</v>
+        <v>6.6298986082408758e-004</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
       <c r="E14">
         <f>E13/SQRT(10)</f>
-        <v>6.4866529633290785E-4</v>
+        <v>6.4866529633290785e-004</v>
       </c>
       <c r="F14">
         <f>F13/SQRT(10)</f>
-        <v>8.2959829636597285E-4</v>
+        <v>8.2959829636597285e-004</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
 </worksheet>
 </file>
--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -3,36 +3,33 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Periodi" sheetId="1" r:id="rId1"/>
-    <sheet name="Intersezione" sheetId="2" r:id="rId2"/>
-    <sheet name="Foglio1" sheetId="3" r:id="rId3"/>
+    <sheet name="Periodi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Intersezione" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Foglio1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t xml:space="preserve">Distanza massa interna (m)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Distanza massa esterna (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">T2 (massa esterna) (s)</t>
+    <t xml:space="preserve">Distanza massa interna (m)</t>
   </si>
   <si>
     <t xml:space="preserve">T1 (coltello 1) (s)</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deviazione standard</t>
+    <t xml:space="preserve">T2 (massa esterna) (s)</t>
   </si>
   <si>
     <t xml:space="preserve">Distanza (m)</t>
@@ -45,6 +42,12 @@
   </si>
   <si>
     <t xml:space="preserve">Errore sulla misura (m)</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deviazione standard</t>
   </si>
   <si>
     <t xml:space="preserve">Errore standard della media</t>
@@ -65,7 +68,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -75,190 +78,240 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="5"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0"/>
+        <bgColor theme="5" tint="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color/>
+        <color auto="1"/>
       </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
-        <color/>
+        <color auto="1"/>
       </right>
       <top style="medium">
-        <color/>
+        <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color/>
-      </bottom>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color/>
+        <color auto="1"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color/>
-      </top>
-      <bottom/>
-      <diagonal/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <left style="none"/>
       <right style="medium">
-        <color/>
+        <color auto="1"/>
       </right>
-      <top style="medium">
-        <color/>
-      </top>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color/>
+        <color auto="1"/>
       </left>
-      <right/>
-      <top/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
-        <color/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
-        <color/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
-      <left/>
+      <left style="none"/>
       <right style="medium">
-        <color/>
+        <color auto="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
-        <color/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color/>
+        <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
-        <color/>
+        <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color/>
+        <color auto="1"/>
       </right>
-      <top style="medium">
-        <color/>
-      </top>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color/>
+        <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color/>
+        <color auto="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
-        <color/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="34">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -602,108 +655,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface="Arial"/>
         <a:cs typeface="Arial"/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface="Arial"/>
         <a:cs typeface="Arial"/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -711,7 +670,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -737,7 +696,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -814,7 +773,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -846,7 +805,7 @@
   </a:themeElements>
   <a:objectDefaults>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -884,309 +843,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2">
         <v>0.12</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="5">
         <v>8.0000000000000002e-002</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="6">
         <v>1.9995000000000001</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="7">
         <v>1.9543999999999999</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="11">
+      <c r="B3" s="5">
         <v>0.10000000000000001</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="6">
         <v>1.9843</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="7">
         <v>1.9044000000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="11">
+      <c r="B4" s="5">
         <v>0.13</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="6">
         <v>1.9690000000000001</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="7">
         <v>1.8761000000000001</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="11">
+      <c r="B5" s="5">
         <v>0.16300000000000001</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="6">
         <v>1.9643999999999999</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="7">
         <v>1.8714</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11">
+      <c r="B6" s="5">
         <v>0.19</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="6">
         <v>1.9528000000000001</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="7">
         <v>1.8234999999999999</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="11">
+      <c r="B7" s="5">
         <v>0.22</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="6">
         <v>1.9461999999999999</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="7">
         <v>1.8037000000000001</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="11">
+      <c r="B8" s="5">
         <v>0.245</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="6">
         <v>1.9360999999999999</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="7">
         <v>1.76</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="11">
+      <c r="B9" s="5">
         <v>0.27000000000000002</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="6">
         <v>1.9354</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="7">
         <v>1.7618</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="11">
+      <c r="B10" s="5">
         <v>0.30499999999999999</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="6">
         <v>1.921</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="7">
         <v>1.7654000000000001</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="11">
+      <c r="B11" s="5">
         <v>0.33700000000000002</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="6">
         <v>1.9114</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="7">
         <v>1.7536</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="11">
+      <c r="B12" s="5">
         <v>0.379</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="6">
         <v>1.903</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="7">
         <v>1.7468999999999999</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="11">
+      <c r="B13" s="5">
         <v>0.41999999999999998</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="6">
         <v>1.9016</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="7">
         <v>1.7565999999999999</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11">
+      <c r="B14" s="5">
         <v>0.46500000000000002</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="6">
         <v>1.8985000000000001</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="7">
         <v>1.7608999999999999</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="11">
+      <c r="B15" s="5">
         <v>0.51000000000000001</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="6">
         <v>1.8929</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="7">
         <v>1.7766</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="11">
+      <c r="B16" s="5">
         <v>0.55500000000000005</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="6">
         <v>1.8799999999999999</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="7">
         <v>1.7897000000000001</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="11">
+      <c r="B17" s="5">
         <v>0.58999999999999997</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="6">
         <v>1.8823000000000001</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="7">
         <v>1.8021</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="11">
+      <c r="B18" s="5">
         <v>0.622</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="6">
         <v>1.8936999999999999</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="7">
         <v>1.8011999999999999</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="11">
+      <c r="B19" s="5">
         <v>0.66300000000000003</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="6">
         <v>1.8996</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="7">
         <v>1.8382000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="11">
+      <c r="B20" s="5">
         <v>0.70499999999999996</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="6">
         <v>1.8989</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="7">
         <v>1.8492999999999999</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="11">
+      <c r="B21" s="5">
         <v>0.73999999999999999</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="6">
         <v>1.9069</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="7">
         <v>1.8694</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="11">
+      <c r="B22" s="5">
         <v>0.77500000000000002</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="6">
         <v>1.9159999999999999</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="7">
         <v>1.8993</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="11">
+      <c r="B23" s="5">
         <v>0.81000000000000005</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="6">
         <v>1.9296</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="7">
         <v>1.9175</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="11">
+      <c r="B24" s="5">
         <v>0.83799999999999997</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="6">
         <v>1.9403999999999999</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="7">
         <v>1.9319</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="11">
+      <c r="B25" s="5">
         <v>0.88200000000000001</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="6">
         <v>1.9753000000000001</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="7">
         <v>1.9626999999999999</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="11">
+      <c r="B26" s="5">
         <v>0.91500000000000004</v>
       </c>
       <c r="C26">
         <v>1.9802999999999999</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="8">
         <v>1.9879</v>
       </c>
     </row>
     <row r="27" ht="14.65">
-      <c r="B27" s="13">
+      <c r="B27" s="9">
         <v>0.92000000000000004</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="10">
         <v>1.9931000000000001</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="11">
         <v>1.9933000000000001</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -1206,257 +1168,260 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="22" t="s">
+    </row>
+    <row r="2" ht="14.65">
+      <c r="A2" s="16">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="B2" s="17">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1.9834000000000001</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.92000000000000004</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1.9897</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="G2" s="9">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="H2" s="18">
+        <v>8.9999999999999997e-002</v>
+      </c>
+      <c r="I2" s="19">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20"/>
+      <c r="B3" s="5">
+        <v>1.9903999999999999</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1.9888999999999999</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="5">
+        <v>1.9885999999999999</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1.9921</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20"/>
+      <c r="B4" s="5">
+        <v>1.9878</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.9869000000000001</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="5">
+        <v>1.9895</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1.9892000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20"/>
+      <c r="B5" s="5">
+        <v>1.9887999999999999</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1.9882</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="5">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1.9832000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20"/>
+      <c r="B6" s="5">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1.9861</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="5">
+        <v>1.9835</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1.9914000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20"/>
+      <c r="B7" s="5">
+        <v>1.9893000000000001</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.99</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="5">
+        <v>1.9898</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1.9901</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20"/>
+      <c r="B8" s="5">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.9866999999999999</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1.9899</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20"/>
+      <c r="B9" s="5">
+        <v>1.9869000000000001</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.9855</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="5">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1.9891000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20"/>
+      <c r="B10" s="5">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1.984</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="5">
+        <v>1.9898</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1.9921</v>
+      </c>
+    </row>
+    <row r="11" ht="14.65">
+      <c r="A11" s="20"/>
+      <c r="B11" s="5">
+        <v>1.9873000000000001</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.9853000000000001</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="5">
+        <v>1.9903999999999999</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1.9881</v>
+      </c>
+    </row>
+    <row r="12" ht="14.65">
+      <c r="A12" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" ht="14.65">
-      <c r="A2" s="17">
-        <v>0.91500000000000004</v>
-      </c>
-      <c r="B2" s="9">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="C2" s="10">
-        <v>1.9834000000000001</v>
-      </c>
-      <c r="D2" s="17">
-        <v>0.92000000000000004</v>
-      </c>
-      <c r="E2" s="11">
-        <v>1.9897</v>
-      </c>
-      <c r="F2" s="10">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="G2" s="13">
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="H2" s="5">
-        <v>8.9999999999999997e-002</v>
-      </c>
-      <c r="I2" s="6">
-        <v>5.0000000000000001e-003</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="11">
-        <v>1.9903999999999999</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1.9888999999999999</v>
-      </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="11">
-        <v>1.9885999999999999</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1.9921</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18"/>
-      <c r="B4" s="11">
-        <v>1.9878</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1.9869000000000001</v>
-      </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="11">
-        <v>1.9895</v>
-      </c>
-      <c r="F4" s="10">
-        <v>1.9892000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18"/>
-      <c r="B5" s="11">
-        <v>1.9887999999999999</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1.9882</v>
-      </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="11">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1.9832000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18"/>
-      <c r="B6" s="11">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1.9861</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="11">
-        <v>1.9835</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1.9914000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18"/>
-      <c r="B7" s="11">
-        <v>1.9893000000000001</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1.99</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="11">
-        <v>1.9898</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1.9901</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18"/>
-      <c r="B8" s="11">
-        <v>1.9886999999999999</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1.9866999999999999</v>
-      </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="11">
-        <v>1.99</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1.9899</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18"/>
-      <c r="B9" s="11">
-        <v>1.9869000000000001</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1.9855</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="11">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="F9" s="10">
-        <v>1.9891000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18"/>
-      <c r="B10" s="11">
-        <v>1.9886999999999999</v>
-      </c>
-      <c r="C10" s="10">
-        <v>1.984</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="11">
-        <v>1.9898</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1.9921</v>
-      </c>
-    </row>
-    <row r="11" ht="14.65">
-      <c r="A11" s="18"/>
-      <c r="B11" s="11">
-        <v>1.9873000000000001</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1.9853000000000001</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="11">
-        <v>1.9903999999999999</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1.9881</v>
-      </c>
-    </row>
-    <row r="12" ht="14.65">
-      <c r="A12" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="B12" s="22">
         <f>AVERAGE(B2:B11)</f>
         <v>1.9887500000000002</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="23">
         <f>AVERAGE(C2:C11)</f>
         <v>1.9864999999999999</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="14">
+      <c r="D12" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="25">
         <f>AVERAGE(E2:E11)</f>
         <v>1.9890900000000002</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="26">
         <f>AVERAGE(F2:F11)</f>
         <v>1.98963</v>
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9">
         <f>_xlfn.STDEV.S(B2:B11)</f>
         <v>1.1993053545003578e-003</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="19">
         <f>_xlfn.STDEV.S(C2:C11)</f>
         <v>2.0965580258021552e-003</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="13">
+      <c r="D13" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="9">
         <f>_xlfn.STDEV.S(E2:E11)</f>
         <v>2.0512597755200563e-003</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="19">
         <f>_xlfn.STDEV.S(F2:F11)</f>
         <v>2.6234201595118625e-003</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -1464,10 +1429,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="22.1328125"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="22.875"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="13.796875"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="18"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="16.59765625"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="22.875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="13.796875"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="18"/>
     <col bestFit="1" customWidth="1" min="7" max="7" width="5.73046875"/>
@@ -1476,280 +1441,283 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="22" t="s">
+    </row>
+    <row r="2" ht="14.65">
+      <c r="A2" s="16">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="B2" s="17">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1.9834000000000001</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.92000000000000004</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1.9897</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="G2" s="9">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="H2" s="18">
+        <v>8.9999999999999997e-002</v>
+      </c>
+      <c r="I2" s="19">
+        <v>5.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20"/>
+      <c r="B3" s="5">
+        <v>1.9903999999999999</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1.9888999999999999</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="5">
+        <v>1.9885999999999999</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1.9921</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20"/>
+      <c r="B4" s="5">
+        <v>1.9878</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.9869000000000001</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="5">
+        <v>1.9895</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1.9892000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20"/>
+      <c r="B5" s="5">
+        <v>1.9887999999999999</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1.9882</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="5">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1.9832000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20"/>
+      <c r="B6" s="5">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1.9861</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="5">
+        <v>1.9835</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1.9914000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20"/>
+      <c r="B7" s="5">
+        <v>1.9893000000000001</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.99</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="5">
+        <v>1.9898</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1.9901</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20"/>
+      <c r="B8" s="5">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.9866999999999999</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1.9899</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20"/>
+      <c r="B9" s="5">
+        <v>1.9869000000000001</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.9855</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="5">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1.9891000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20"/>
+      <c r="B10" s="5">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1.984</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="5">
+        <v>1.9898</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1.9921</v>
+      </c>
+    </row>
+    <row r="11" ht="14.65">
+      <c r="A11" s="20"/>
+      <c r="B11" s="5">
+        <v>1.9873000000000001</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.9853000000000001</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="5">
+        <v>1.9903999999999999</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1.9881</v>
+      </c>
+    </row>
+    <row r="12" ht="14.65">
+      <c r="A12" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" ht="14.65">
-      <c r="A2" s="17">
-        <v>0.91500000000000004</v>
-      </c>
-      <c r="B2" s="9">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="C2" s="10">
-        <v>1.9834000000000001</v>
-      </c>
-      <c r="D2" s="17">
-        <v>0.92000000000000004</v>
-      </c>
-      <c r="E2" s="11">
-        <v>1.9897</v>
-      </c>
-      <c r="F2" s="10">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="G2" s="13">
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="H2" s="5">
-        <v>8.9999999999999997e-002</v>
-      </c>
-      <c r="I2" s="6">
-        <v>5.0000000000000001e-003</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="11">
-        <v>1.9903999999999999</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1.9888999999999999</v>
-      </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="11">
-        <v>1.9885999999999999</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1.9921</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="18"/>
-      <c r="B4" s="11">
-        <v>1.9878</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1.9869000000000001</v>
-      </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="11">
-        <v>1.9895</v>
-      </c>
-      <c r="F4" s="10">
-        <v>1.9892000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18"/>
-      <c r="B5" s="11">
-        <v>1.9887999999999999</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1.9882</v>
-      </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="11">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1.9832000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18"/>
-      <c r="B6" s="11">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1.9861</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="11">
-        <v>1.9835</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1.9914000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18"/>
-      <c r="B7" s="11">
-        <v>1.9893000000000001</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1.99</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="11">
-        <v>1.9898</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1.9901</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18"/>
-      <c r="B8" s="11">
-        <v>1.9886999999999999</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1.9866999999999999</v>
-      </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="11">
-        <v>1.99</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1.9899</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18"/>
-      <c r="B9" s="11">
-        <v>1.9869000000000001</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1.9855</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="11">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="F9" s="10">
-        <v>1.9891000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="18"/>
-      <c r="B10" s="11">
-        <v>1.9886999999999999</v>
-      </c>
-      <c r="C10" s="10">
-        <v>1.984</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="11">
-        <v>1.9898</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1.9921</v>
-      </c>
-    </row>
-    <row r="11" ht="14.65">
-      <c r="A11" s="18"/>
-      <c r="B11" s="11">
-        <v>1.9873000000000001</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1.9853000000000001</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="11">
-        <v>1.9903999999999999</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1.9881</v>
-      </c>
-    </row>
-    <row r="12" ht="14.65">
-      <c r="A12" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="12">
+      <c r="B12" s="22">
         <f>AVERAGE(B2:B11)</f>
         <v>1.9887500000000002</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="23">
         <f>AVERAGE(C2:C11)</f>
         <v>1.9864999999999999</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="14">
+      <c r="D12" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="25">
         <f>AVERAGE(E2:E11)</f>
         <v>1.9890900000000002</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="26">
         <f>AVERAGE(F2:F11)</f>
         <v>1.98963</v>
       </c>
     </row>
     <row r="13" ht="14.65">
-      <c r="A13" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5">
         <f>_xlfn.STDEV.S(B2:B11)</f>
         <v>1.1993053545003578e-003</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="8">
         <f>_xlfn.STDEV.S(C2:C11)</f>
         <v>2.0965580258021552e-003</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="13">
+      <c r="D13" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5">
         <f>_xlfn.STDEV.S(E2:E11)</f>
         <v>2.0512597755200563e-003</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="8">
         <f>_xlfn.STDEV.S(F2:F11)</f>
         <v>2.6234201595118625e-003</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="31">
         <f>B13/SQRT(10)</f>
         <v>3.7925365302567999e-004</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="32">
         <f>C13/SQRT(10)</f>
         <v>6.6298986082408758e-004</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="31">
         <f>E13/SQRT(10)</f>
         <v>6.4866529633290785e-004</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="32">
         <f>F13/SQRT(10)</f>
         <v>8.2959829636597285e-004</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C502C29-A804-4BA8-B718-C7AD7104DBF7}"/>
+  <xr:revisionPtr revIDLastSave="328" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D85C1FF0-5369-455D-87E8-FC4E1CF3ABC8}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
     <sheet name="Intersezione" sheetId="2" r:id="rId2"/>
     <sheet name="Foglio1" sheetId="3" r:id="rId3"/>
+    <sheet name="Caduta libera" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="13">
   <si>
     <t>Distanza massa interna (m)</t>
   </si>
@@ -74,6 +75,12 @@
   </si>
   <si>
     <t>Errore standard della media</t>
+  </si>
+  <si>
+    <t>Tempi (s)</t>
+  </si>
+  <si>
+    <t>Errore della media</t>
   </si>
 </sst>
 </file>
@@ -112,7 +119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -252,11 +259,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -286,6 +319,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1505,4 +1544,429 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D1EB1E-FDEB-4EAA-996C-BB53E06F9A9A}">
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.9296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="B2" s="10">
+        <v>0.14330000000000001</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="10">
+        <v>0.16980000000000001</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.19339999999999999</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="J2" s="10">
+        <v>0.23419999999999999</v>
+      </c>
+      <c r="K2" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="L2" s="10">
+        <v>0.25280000000000002</v>
+      </c>
+      <c r="M2" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="N2" s="10">
+        <v>0.27129999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" s="11"/>
+      <c r="B3" s="10">
+        <v>0.1434</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10">
+        <v>0.1716</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="10">
+        <v>0.19320000000000001</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10">
+        <v>0.215</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="10">
+        <v>0.2344</v>
+      </c>
+      <c r="K3" s="11"/>
+      <c r="L3" s="10">
+        <v>0.253</v>
+      </c>
+      <c r="M3" s="11"/>
+      <c r="N3" s="10">
+        <v>0.27189999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4" s="11"/>
+      <c r="B4" s="10">
+        <v>0.14330000000000001</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="10">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="10">
+        <v>0.1933</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10">
+        <v>0.21490000000000001</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="10">
+        <v>0.23430000000000001</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="10">
+        <v>0.25369999999999998</v>
+      </c>
+      <c r="M4" s="11"/>
+      <c r="N4" s="10">
+        <v>0.27210000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5" s="11"/>
+      <c r="B5" s="10">
+        <v>0.1431</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10">
+        <v>0.17030000000000001</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="10">
+        <v>0.1933</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10">
+        <v>0.21479999999999999</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="10">
+        <v>0.23419999999999999</v>
+      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="10">
+        <v>0.25319999999999998</v>
+      </c>
+      <c r="M5" s="11"/>
+      <c r="N5" s="10">
+        <v>0.27079999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6" s="11"/>
+      <c r="B6" s="10">
+        <v>0.14319999999999999</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="10">
+        <v>0.1706</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="10">
+        <v>0.1933</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10">
+        <v>0.2152</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="10">
+        <v>0.2344</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="10">
+        <v>0.25359999999999999</v>
+      </c>
+      <c r="M6" s="11"/>
+      <c r="N6" s="10">
+        <v>0.27179999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7" s="11"/>
+      <c r="B7" s="10">
+        <v>0.14330000000000001</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10">
+        <v>0.1711</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="10">
+        <v>0.19359999999999999</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10">
+        <v>0.2147</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="10">
+        <v>0.23449999999999999</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="10">
+        <v>0.253</v>
+      </c>
+      <c r="M7" s="11"/>
+      <c r="N7" s="10">
+        <v>0.26860000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8" s="11"/>
+      <c r="B8" s="10">
+        <v>0.1431</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="10">
+        <v>0.19359999999999999</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10">
+        <v>0.21479999999999999</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="10">
+        <v>0.23430000000000001</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="10">
+        <v>0.25340000000000001</v>
+      </c>
+      <c r="M8" s="11"/>
+      <c r="N8" s="10">
+        <v>0.26829999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="30">
+        <f>AVERAGE(B2:B8)</f>
+        <v>0.14324285714285714</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="30">
+        <f t="shared" ref="D9" si="0">AVERAGE(D2:D8)</f>
+        <v>0.17062857142857141</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="30">
+        <f t="shared" ref="F9" si="1">AVERAGE(F2:F8)</f>
+        <v>0.19338571428571427</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="30">
+        <f>AVERAGE(H2:H8)</f>
+        <v>0.21485714285714286</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="30">
+        <f t="shared" ref="J9" si="2">AVERAGE(J2:J8)</f>
+        <v>0.23432857142857141</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="30">
+        <f t="shared" ref="L9" si="3">AVERAGE(L2:L8)</f>
+        <v>0.25324285714285721</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="30">
+        <f t="shared" ref="N9" si="4">AVERAGE(N2:N8)</f>
+        <v>0.27068571428571425</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="34">
+        <f>_xlfn.STDEV.S(B2:B8)/SQRT(7)</f>
+        <v>4.2857142857143202E-5</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="34">
+        <f t="shared" ref="D10:N10" si="5">_xlfn.STDEV.S(D2:D8)/SQRT(7)</f>
+        <v>2.4369603013188476E-4</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="34">
+        <f t="shared" ref="F10:N10" si="6">_xlfn.STDEV.S(F2:F8)/SQRT(7)</f>
+        <v>5.9476171413316292E-5</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="34">
+        <f t="shared" ref="H10:N10" si="7">_xlfn.STDEV.S(H2:H8)/SQRT(7)</f>
+        <v>7.514158970504462E-5</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="34">
+        <f t="shared" ref="J10:N10" si="8">_xlfn.STDEV.S(J2:J8)/SQRT(7)</f>
+        <v>4.2056004125370102E-5</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="34">
+        <f t="shared" ref="L10:N10" si="9">_xlfn.STDEV.S(L2:L8)/SQRT(7)</f>
+        <v>1.2697420596164739E-4</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N10" s="34">
+        <f t="shared" ref="N10" si="10">_xlfn.STDEV.S(N2:N8)/SQRT(7)</f>
+        <v>6.0056662586997192E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="328" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D85C1FF0-5369-455D-87E8-FC4E1CF3ABC8}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A2AF15B-7BCE-407F-8B4B-43CF7E29CCFB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
-    <sheet name="Intersezione" sheetId="2" r:id="rId2"/>
-    <sheet name="Foglio1" sheetId="3" r:id="rId3"/>
-    <sheet name="Caduta libera" sheetId="4" r:id="rId4"/>
+    <sheet name="Intersezione" sheetId="3" r:id="rId2"/>
+    <sheet name="Caduta libera" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="13">
   <si>
     <t>Distanza massa interna (m)</t>
   </si>
@@ -322,9 +321,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -981,277 +980,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2331EE30-F3F4-48C6-BC63-D4000596DD25}">
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.46484375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="17">
-        <v>0.91500000000000004</v>
-      </c>
-      <c r="B2" s="9">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="C2" s="10">
-        <v>1.9834000000000001</v>
-      </c>
-      <c r="D2" s="17">
-        <v>0.92</v>
-      </c>
-      <c r="E2" s="11">
-        <v>1.9897</v>
-      </c>
-      <c r="F2" s="10">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="G2" s="13">
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="I2" s="6">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="18"/>
-      <c r="B3" s="11">
-        <v>1.9903999999999999</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1.9888999999999999</v>
-      </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="11">
-        <v>1.9885999999999999</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1.9921</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="18"/>
-      <c r="B4" s="11">
-        <v>1.9878</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1.9869000000000001</v>
-      </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="11">
-        <v>1.9895</v>
-      </c>
-      <c r="F4" s="10">
-        <v>1.9892000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="18"/>
-      <c r="B5" s="11">
-        <v>1.9887999999999999</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1.9882</v>
-      </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="11">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1.9832000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="18"/>
-      <c r="B6" s="11">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1.9861</v>
-      </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="11">
-        <v>1.9835</v>
-      </c>
-      <c r="F6" s="10">
-        <v>1.9914000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="18"/>
-      <c r="B7" s="11">
-        <v>1.9893000000000001</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1.99</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="11">
-        <v>1.9898</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1.9901</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="18"/>
-      <c r="B8" s="11">
-        <v>1.9886999999999999</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1.9866999999999999</v>
-      </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="11">
-        <v>1.99</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1.9899</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="18"/>
-      <c r="B9" s="11">
-        <v>1.9869000000000001</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1.9855</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="11">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="F9" s="10">
-        <v>1.9891000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="18"/>
-      <c r="B10" s="11">
-        <v>1.9886999999999999</v>
-      </c>
-      <c r="C10" s="10">
-        <v>1.984</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="11">
-        <v>1.9898</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1.9921</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="18"/>
-      <c r="B11" s="11">
-        <v>1.9873000000000001</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1.9853000000000001</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="11">
-        <v>1.9903999999999999</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1.9881</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="12">
-        <f>AVERAGE(B2:B11)</f>
-        <v>1.9887500000000002</v>
-      </c>
-      <c r="C12" s="3">
-        <f>AVERAGE(C2:C11)</f>
-        <v>1.9864999999999999</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="14">
-        <f>AVERAGE(E2:E11)</f>
-        <v>1.9890900000000002</v>
-      </c>
-      <c r="F12" s="15">
-        <f>AVERAGE(F2:F11)</f>
-        <v>1.98963</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="13">
-        <f>_xlfn.STDEV.S(B2:B11)</f>
-        <v>1.1993053545003578E-3</v>
-      </c>
-      <c r="C13" s="6">
-        <f>_xlfn.STDEV.S(C2:C11)</f>
-        <v>2.0965580258021552E-3</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="13">
-        <f>_xlfn.STDEV.S(E2:E11)</f>
-        <v>2.0512597755200563E-3</v>
-      </c>
-      <c r="F13" s="6">
-        <f>_xlfn.STDEV.S(F2:F11)</f>
-        <v>2.6234201595118625E-3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A3B4CE-F596-452E-9DD8-1E4854DB4C41}">
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1546,7 +1274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D1EB1E-FDEB-4EAA-996C-BB53E06F9A9A}">
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1556,7 +1284,7 @@
     <col min="3" max="3" width="10.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.59765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.46484375" customWidth="1"/>
     <col min="8" max="8" width="11.73046875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.73046875" bestFit="1" customWidth="1"/>
@@ -1565,46 +1293,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="M1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="34" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1887,49 +1615,49 @@
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="32">
         <f>_xlfn.STDEV.S(B2:B8)/SQRT(7)</f>
         <v>4.2857142857143202E-5</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="32">
         <f t="shared" ref="D10:N10" si="5">_xlfn.STDEV.S(D2:D8)/SQRT(7)</f>
         <v>2.4369603013188476E-4</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="32">
         <f t="shared" ref="F10:N10" si="6">_xlfn.STDEV.S(F2:F8)/SQRT(7)</f>
         <v>5.9476171413316292E-5</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="32">
         <f t="shared" ref="H10:N10" si="7">_xlfn.STDEV.S(H2:H8)/SQRT(7)</f>
         <v>7.514158970504462E-5</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="32">
         <f t="shared" ref="J10:N10" si="8">_xlfn.STDEV.S(J2:J8)/SQRT(7)</f>
         <v>4.2056004125370102E-5</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="32">
         <f t="shared" ref="L10:N10" si="9">_xlfn.STDEV.S(L2:L8)/SQRT(7)</f>
         <v>1.2697420596164739E-4</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="32">
         <f t="shared" ref="N10" si="10">_xlfn.STDEV.S(N2:N8)/SQRT(7)</f>
         <v>6.0056662586997192E-4</v>
       </c>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A2AF15B-7BCE-407F-8B4B-43CF7E29CCFB}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="8_{19C89E71-1DD8-47E7-B68E-0E1E8817402E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF0B120-27C3-4590-8AC1-CB7970C97477}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{3B2BD29B-AF11-4365-A6A6-128F74E5E299}"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" r:id="rId1"/>
     <sheet name="Intersezione" sheetId="3" r:id="rId2"/>
     <sheet name="Caduta libera" sheetId="4" r:id="rId3"/>
+    <sheet name="Foglio1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
   <si>
     <t>Distanza massa interna (m)</t>
   </si>
@@ -81,13 +82,17 @@
   <si>
     <t>Errore della media</t>
   </si>
+  <si>
+    <t>1,99071,989</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="172" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -288,10 +293,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -320,10 +324,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -675,13 +679,13 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
@@ -689,288 +693,288 @@
       <c r="A2">
         <v>0.12</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>0.08</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="24">
         <v>1.9995000000000001</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="25">
         <v>1.9543999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>0.1</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="24">
         <v>1.9843</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="25">
         <v>1.9044000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <v>0.13</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="24">
         <v>1.9690000000000001</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="25">
         <v>1.8761000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>0.16300000000000001</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="24">
         <v>1.9643999999999999</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="25">
         <v>1.8714</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <v>0.19</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>1.9528000000000001</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="25">
         <v>1.8234999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>0.22</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>1.9461999999999999</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="25">
         <v>1.8037000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <v>0.245</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="24">
         <v>1.9360999999999999</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1.76</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>0.27</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <v>1.9354</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="25">
         <v>1.7618</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <v>0.30499999999999999</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="24">
         <v>1.921</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="25">
         <v>1.7654000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>0.33700000000000002</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <v>1.9114</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="25">
         <v>1.7536</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <v>0.379</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="24">
         <v>1.903</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="25">
         <v>1.7468999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>0.42</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>1.9016</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="25">
         <v>1.7565999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <v>0.46500000000000002</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>1.8985000000000001</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <v>1.7608999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>0.51</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>1.8929</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="25">
         <v>1.7766</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <v>0.55500000000000005</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>1.88</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="25">
         <v>1.7897000000000001</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>0.59</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>1.8823000000000001</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="25">
         <v>1.8021</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <v>0.622</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="24">
         <v>1.8936999999999999</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="25">
         <v>1.8011999999999999</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>0.66300000000000003</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <v>1.8996</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="25">
         <v>1.8382000000000001</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <v>0.70499999999999996</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>1.8989</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="25">
         <v>1.8492999999999999</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>0.74</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>1.9069</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="25">
         <v>1.8694</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <v>0.77500000000000002</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="24">
         <v>1.9159999999999999</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="25">
         <v>1.8993</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>0.81</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="24">
         <v>1.9296</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="25">
         <v>1.9175</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <v>0.83799999999999997</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="24">
         <v>1.9403999999999999</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="25">
         <v>1.9319</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>0.88200000000000001</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="24">
         <v>1.9753000000000001</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="25">
         <v>1.9626999999999999</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <v>0.91500000000000004</v>
       </c>
       <c r="C26">
         <v>1.9802999999999999</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>1.9879</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="13">
+      <c r="B27" s="12">
         <v>0.92</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <v>1.9931000000000001</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="27">
         <v>1.9933000000000001</v>
       </c>
     </row>
@@ -981,7 +985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A3B4CE-F596-452E-9DD8-1E4854DB4C41}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
@@ -996,277 +1000,513 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="22" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="17">
+      <c r="A2" s="16">
         <v>0.91500000000000004</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>1.9890000000000001</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <v>1.9834000000000001</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="16">
         <v>0.92</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <v>1.9897</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <v>1.9911000000000001</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="4">
         <v>1.0049999999999999</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>0.09</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="18"/>
-      <c r="B3" s="11">
+      <c r="A3" s="17"/>
+      <c r="B3" s="10">
         <v>1.9903999999999999</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>1.9888999999999999</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="11">
+      <c r="D3" s="17"/>
+      <c r="E3" s="10">
         <v>1.9885999999999999</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>1.9921</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="18"/>
-      <c r="B4" s="11">
+      <c r="A4" s="17"/>
+      <c r="B4" s="10">
         <v>1.9878</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>1.9869000000000001</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="11">
+      <c r="D4" s="17"/>
+      <c r="E4" s="10">
         <v>1.9895</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>1.9892000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="18"/>
-      <c r="B5" s="11">
+      <c r="A5" s="17"/>
+      <c r="B5" s="10">
         <v>1.9887999999999999</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>1.9882</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="11">
+      <c r="D5" s="17"/>
+      <c r="E5" s="10">
         <v>1.9890000000000001</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>1.9832000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="18"/>
-      <c r="B6" s="11">
+      <c r="A6" s="17"/>
+      <c r="B6" s="10">
         <v>1.9905999999999999</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>1.9861</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="11">
+      <c r="D6" s="17"/>
+      <c r="E6" s="10">
         <v>1.9835</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>1.9914000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="18"/>
-      <c r="B7" s="11">
+      <c r="A7" s="17"/>
+      <c r="B7" s="10">
         <v>1.9893000000000001</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>1.99</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="11">
+      <c r="D7" s="17"/>
+      <c r="E7" s="10">
         <v>1.9898</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>1.9901</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8" s="18"/>
-      <c r="B8" s="11">
+      <c r="A8" s="17"/>
+      <c r="B8" s="10">
         <v>1.9886999999999999</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>1.9866999999999999</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="11">
+      <c r="D8" s="17"/>
+      <c r="E8" s="10">
         <v>1.99</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>1.9899</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A9" s="18"/>
-      <c r="B9" s="11">
+      <c r="A9" s="17"/>
+      <c r="B9" s="10">
         <v>1.9869000000000001</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>1.9855</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="11">
+      <c r="D9" s="17"/>
+      <c r="E9" s="10">
         <v>1.9905999999999999</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>1.9891000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="18"/>
-      <c r="B10" s="11">
+      <c r="A10" s="17"/>
+      <c r="B10" s="10">
         <v>1.9886999999999999</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>1.984</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="11">
+      <c r="D10" s="17"/>
+      <c r="E10" s="10">
         <v>1.9898</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>1.9921</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="18"/>
-      <c r="B11" s="11">
+      <c r="A11" s="17"/>
+      <c r="B11" s="10">
         <v>1.9873000000000001</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>1.9853000000000001</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="11">
+      <c r="D11" s="17"/>
+      <c r="E11" s="10">
         <v>1.9903999999999999</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>1.9881</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <f>AVERAGE(B2:B11)</f>
         <v>1.9887500000000002</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <f>AVERAGE(C2:C11)</f>
         <v>1.9864999999999999</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <f>AVERAGE(E2:E11)</f>
         <v>1.9890900000000002</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <f>AVERAGE(F2:F11)</f>
         <v>1.98963</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <f>_xlfn.STDEV.S(B2:B11)</f>
         <v>1.1993053545003578E-3</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <f>_xlfn.STDEV.S(C2:C11)</f>
         <v>2.0965580258021552E-3</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f>_xlfn.STDEV.S(E2:E11)</f>
         <v>2.0512597755200563E-3</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <f>_xlfn.STDEV.S(F2:F11)</f>
         <v>2.6234201595118625E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="4">
         <f>B13/SQRT(10)</f>
         <v>3.7925365302567999E-4</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="4">
         <f>C13/SQRT(10)</f>
         <v>6.6298986082408758E-4</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="4">
         <f>E13/SQRT(10)</f>
         <v>6.4866529633290785E-4</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="5">
         <f>F13/SQRT(10)</f>
         <v>8.2959829636597285E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" s="16">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="9">
+        <v>1.9875</v>
+      </c>
+      <c r="D15" s="16">
+        <v>0.92</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1.9866999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" s="17"/>
+      <c r="B16" s="10">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1.9873000000000001</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="10">
+        <v>1.9863</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1.9923999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="17"/>
+      <c r="B17" s="10">
+        <v>1.9908999999999999</v>
+      </c>
+      <c r="C17" s="9">
+        <v>1.9894000000000001</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="10">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1.9919</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="17"/>
+      <c r="B18" s="10">
+        <v>1.9919</v>
+      </c>
+      <c r="C18" s="9">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="10">
+        <v>1.9857</v>
+      </c>
+      <c r="F18" s="9">
+        <v>1.9925999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="17"/>
+      <c r="B19" s="10">
+        <v>1.9908999999999999</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1.9882</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="10">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F19" s="9">
+        <v>1.9903999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="17"/>
+      <c r="B20" s="10">
+        <v>1.9906999999999999</v>
+      </c>
+      <c r="C20" s="9">
+        <v>1.9882</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="10">
+        <v>1.9925999999999999</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1.9904999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="17"/>
+      <c r="B21" s="10">
+        <v>1.9913000000000001</v>
+      </c>
+      <c r="C21" s="9">
+        <v>1.988</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="10">
+        <v>1.9928999999999999</v>
+      </c>
+      <c r="F21" s="9">
+        <v>1.9907999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="17"/>
+      <c r="B22" s="10">
+        <v>1.9904999999999999</v>
+      </c>
+      <c r="C22" s="9">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="10">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1.9937</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="17"/>
+      <c r="B23" s="10">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="C23" s="9">
+        <v>1.9879</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="10">
+        <v>1.982</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="17"/>
+      <c r="B24" s="10">
+        <v>1.9923</v>
+      </c>
+      <c r="C24" s="9">
+        <v>1.9870000000000001</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="10">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1.9839</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="11">
+        <f>AVERAGE(B15:B24)</f>
+        <v>1.9911333333333334</v>
+      </c>
+      <c r="C25" s="2">
+        <f>AVERAGE(C15:C24)</f>
+        <v>1.9881199999999999</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="13">
+        <f>AVERAGE(E15:E24)</f>
+        <v>1.9893800000000001</v>
+      </c>
+      <c r="F25" s="14">
+        <f>AVERAGE(F15:F24)</f>
+        <v>1.9902899999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="12">
+        <f>_xlfn.STDEV.S(B15:B24)</f>
+        <v>6.0827625302984929E-4</v>
+      </c>
+      <c r="C26" s="5">
+        <f>_xlfn.STDEV.S(C15:C24)</f>
+        <v>7.554248252914698E-4</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="12">
+        <f>_xlfn.STDEV.S(E15:E24)</f>
+        <v>3.5187750393819938E-3</v>
+      </c>
+      <c r="F26" s="5">
+        <f>_xlfn.STDEV.S(F15:F24)</f>
+        <v>2.9463536787018665E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <f>B26/SQRT(10)</f>
+        <v>1.9235384061672207E-4</v>
+      </c>
+      <c r="C27">
+        <f>C26/SQRT(10)</f>
+        <v>2.3888630489558158E-4</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27">
+        <f>E26/SQRT(10)</f>
+        <v>1.1127343698195788E-3</v>
+      </c>
+      <c r="F27">
+        <f>F26/SQRT(10)</f>
+        <v>9.3171884171138343E-4</v>
       </c>
     </row>
   </sheetData>
@@ -1276,11 +1516,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D1EB1E-FDEB-4EAA-996C-BB53E06F9A9A}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.46484375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.59765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.73046875" bestFit="1" customWidth="1"/>
@@ -1293,406 +1533,647 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="34" t="s">
+      <c r="L1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="34" t="s">
+      <c r="N1" s="32" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>0.15</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="10">
         <v>0.2</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>0.16980000000000001</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <v>0.25</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <v>0.19339999999999999</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <v>0.3</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <v>0.21460000000000001</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0.35</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="9">
         <v>0.23419999999999999</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <v>0.4</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="9">
         <v>0.25280000000000002</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <v>0.45</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="9">
         <v>0.27129999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" s="11"/>
-      <c r="B3" s="10">
+      <c r="A3" s="10"/>
+      <c r="B3" s="9">
         <v>0.1434</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10">
+      <c r="C3" s="10"/>
+      <c r="D3" s="9">
         <v>0.1716</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="10">
+      <c r="E3" s="10"/>
+      <c r="F3" s="9">
         <v>0.19320000000000001</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10">
+      <c r="G3" s="10"/>
+      <c r="H3" s="9">
         <v>0.215</v>
       </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="10">
+      <c r="I3" s="10"/>
+      <c r="J3" s="9">
         <v>0.2344</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="10">
+      <c r="K3" s="10"/>
+      <c r="L3" s="9">
         <v>0.253</v>
       </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="10">
+      <c r="M3" s="10"/>
+      <c r="N3" s="9">
         <v>0.27189999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" s="11"/>
-      <c r="B4" s="10">
+      <c r="A4" s="10"/>
+      <c r="B4" s="9">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="10">
+      <c r="C4" s="10"/>
+      <c r="D4" s="9">
         <v>0.17100000000000001</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="10">
+      <c r="E4" s="10"/>
+      <c r="F4" s="9">
         <v>0.1933</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="10">
+      <c r="G4" s="10"/>
+      <c r="H4" s="9">
         <v>0.21490000000000001</v>
       </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="10">
+      <c r="I4" s="10"/>
+      <c r="J4" s="9">
         <v>0.23430000000000001</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="10">
+      <c r="K4" s="10"/>
+      <c r="L4" s="9">
         <v>0.25369999999999998</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="10">
+      <c r="M4" s="10"/>
+      <c r="N4" s="9">
         <v>0.27210000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" s="11"/>
-      <c r="B5" s="10">
+      <c r="A5" s="10"/>
+      <c r="B5" s="9">
         <v>0.1431</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10">
+      <c r="C5" s="10"/>
+      <c r="D5" s="9">
         <v>0.17030000000000001</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="10">
+      <c r="E5" s="10"/>
+      <c r="F5" s="9">
         <v>0.1933</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="10">
+      <c r="G5" s="10"/>
+      <c r="H5" s="9">
         <v>0.21479999999999999</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="10">
+      <c r="I5" s="10"/>
+      <c r="J5" s="9">
         <v>0.23419999999999999</v>
       </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="10">
+      <c r="K5" s="10"/>
+      <c r="L5" s="9">
         <v>0.25319999999999998</v>
       </c>
-      <c r="M5" s="11"/>
-      <c r="N5" s="10">
+      <c r="M5" s="10"/>
+      <c r="N5" s="9">
         <v>0.27079999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" s="11"/>
-      <c r="B6" s="10">
+      <c r="A6" s="10"/>
+      <c r="B6" s="9">
         <v>0.14319999999999999</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="10">
+      <c r="C6" s="10"/>
+      <c r="D6" s="9">
         <v>0.1706</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="10">
+      <c r="E6" s="10"/>
+      <c r="F6" s="9">
         <v>0.1933</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="10">
+      <c r="G6" s="10"/>
+      <c r="H6" s="9">
         <v>0.2152</v>
       </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="10">
+      <c r="I6" s="10"/>
+      <c r="J6" s="9">
         <v>0.2344</v>
       </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="10">
+      <c r="K6" s="10"/>
+      <c r="L6" s="9">
         <v>0.25359999999999999</v>
       </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="10">
+      <c r="M6" s="10"/>
+      <c r="N6" s="9">
         <v>0.27179999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="11"/>
-      <c r="B7" s="10">
+      <c r="A7" s="10"/>
+      <c r="B7" s="9">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10">
+      <c r="C7" s="10"/>
+      <c r="D7" s="9">
         <v>0.1711</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="10">
+      <c r="E7" s="10"/>
+      <c r="F7" s="9">
         <v>0.19359999999999999</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="10">
+      <c r="G7" s="10"/>
+      <c r="H7" s="9">
         <v>0.2147</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="10">
+      <c r="I7" s="10"/>
+      <c r="J7" s="9">
         <v>0.23449999999999999</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="10">
+      <c r="K7" s="10"/>
+      <c r="L7" s="9">
         <v>0.253</v>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="10">
+      <c r="M7" s="10"/>
+      <c r="N7" s="9">
         <v>0.26860000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10">
+      <c r="A8" s="10"/>
+      <c r="B8" s="9">
         <v>0.1431</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10">
+      <c r="C8" s="10"/>
+      <c r="D8" s="9">
         <v>0.17</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="10">
+      <c r="E8" s="10"/>
+      <c r="F8" s="9">
         <v>0.19359999999999999</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="10">
+      <c r="G8" s="10"/>
+      <c r="H8" s="9">
         <v>0.21479999999999999</v>
       </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="10">
+      <c r="I8" s="10"/>
+      <c r="J8" s="9">
         <v>0.23430000000000001</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="10">
+      <c r="K8" s="10"/>
+      <c r="L8" s="9">
         <v>0.25340000000000001</v>
       </c>
-      <c r="M8" s="11"/>
-      <c r="N8" s="10">
+      <c r="M8" s="10"/>
+      <c r="N8" s="9">
         <v>0.26829999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>AVERAGE(B2:B8)</f>
         <v>0.14324285714285714</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="30">
-        <f t="shared" ref="D9" si="0">AVERAGE(D2:D8)</f>
+      <c r="D9" s="29">
+        <f>AVERAGE(D2:D8)</f>
         <v>0.17062857142857141</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="30">
-        <f t="shared" ref="F9" si="1">AVERAGE(F2:F8)</f>
+      <c r="F9" s="29">
+        <f>AVERAGE(F2:F8)</f>
         <v>0.19338571428571427</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="29">
         <f>AVERAGE(H2:H8)</f>
         <v>0.21485714285714286</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="J9" s="30">
-        <f t="shared" ref="J9" si="2">AVERAGE(J2:J8)</f>
+      <c r="J9" s="29">
+        <f t="shared" ref="J9" si="0">AVERAGE(J2:J8)</f>
         <v>0.23432857142857141</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="L9" s="30">
-        <f t="shared" ref="L9" si="3">AVERAGE(L2:L8)</f>
+      <c r="L9" s="29">
+        <f t="shared" ref="L9" si="1">AVERAGE(L2:L8)</f>
         <v>0.25324285714285721</v>
       </c>
-      <c r="M9" s="29" t="s">
+      <c r="M9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="30">
-        <f t="shared" ref="N9" si="4">AVERAGE(N2:N8)</f>
+      <c r="N9" s="29">
+        <f t="shared" ref="N9" si="2">AVERAGE(N2:N8)</f>
         <v>0.27068571428571425</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>_xlfn.STDEV.S(B2:B8)/SQRT(7)</f>
         <v>4.2857142857143202E-5</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="32">
-        <f t="shared" ref="D10:N10" si="5">_xlfn.STDEV.S(D2:D8)/SQRT(7)</f>
+      <c r="D10" s="30">
+        <f t="shared" ref="D10" si="3">_xlfn.STDEV.S(D2:D8)/SQRT(7)</f>
         <v>2.4369603013188476E-4</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="32">
-        <f t="shared" ref="F10:N10" si="6">_xlfn.STDEV.S(F2:F8)/SQRT(7)</f>
+      <c r="F10" s="30">
+        <f t="shared" ref="F10" si="4">_xlfn.STDEV.S(F2:F8)/SQRT(7)</f>
         <v>5.9476171413316292E-5</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="32">
-        <f t="shared" ref="H10:N10" si="7">_xlfn.STDEV.S(H2:H8)/SQRT(7)</f>
+      <c r="H10" s="30">
+        <f t="shared" ref="H10" si="5">_xlfn.STDEV.S(H2:H8)/SQRT(7)</f>
         <v>7.514158970504462E-5</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="32">
-        <f t="shared" ref="J10:N10" si="8">_xlfn.STDEV.S(J2:J8)/SQRT(7)</f>
+      <c r="J10" s="30">
+        <f t="shared" ref="J10" si="6">_xlfn.STDEV.S(J2:J8)/SQRT(7)</f>
         <v>4.2056004125370102E-5</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="32">
-        <f t="shared" ref="L10:N10" si="9">_xlfn.STDEV.S(L2:L8)/SQRT(7)</f>
+      <c r="L10" s="30">
+        <f t="shared" ref="L10" si="7">_xlfn.STDEV.S(L2:L8)/SQRT(7)</f>
         <v>1.2697420596164739E-4</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N10" s="32">
-        <f t="shared" ref="N10" si="10">_xlfn.STDEV.S(N2:N8)/SQRT(7)</f>
+      <c r="N10" s="30">
+        <f t="shared" ref="N10" si="8">_xlfn.STDEV.S(N2:N8)/SQRT(7)</f>
         <v>6.0056662586997192E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A12" s="31"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006248A2-9A8A-40C9-B211-C9A7020F8921}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="22.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="16">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1.9875</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.92</v>
+      </c>
+      <c r="E2" s="10">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1.9866999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="17"/>
+      <c r="B3" s="10">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1.9873000000000001</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="E3" s="10">
+        <v>1.9863</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1.9923999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="17"/>
+      <c r="B4" s="10">
+        <v>1.9908999999999999</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1.9894000000000001</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="10">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1.9919</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="17"/>
+      <c r="B5" s="10">
+        <v>1.9919</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="10">
+        <v>1.9857</v>
+      </c>
+      <c r="F5" s="9">
+        <v>1.9925999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="17"/>
+      <c r="B6" s="10">
+        <v>1.9908999999999999</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1.9882</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="10">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1.9903999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="17"/>
+      <c r="B7" s="10">
+        <v>1.9906999999999999</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1.9882</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="10">
+        <v>1.9925999999999999</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1.9904999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="17"/>
+      <c r="B8" s="10">
+        <v>1.9913000000000001</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1.988</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="10">
+        <v>1.9928999999999999</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1.9907999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="17"/>
+      <c r="B9" s="10">
+        <v>1.9904999999999999</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="10">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F9" s="9">
+        <v>1.9937</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="17"/>
+      <c r="B10" s="10">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1.9879</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="10">
+        <v>1.982</v>
+      </c>
+      <c r="F10" s="9">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="17"/>
+      <c r="B11" s="10">
+        <v>1.9923</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1.9870000000000001</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="10">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="F11" s="9">
+        <v>1.9839</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="11">
+        <f>AVERAGE(B2:B11)</f>
+        <v>1.9911333333333334</v>
+      </c>
+      <c r="C12" s="2">
+        <f>AVERAGE(C2:C11)</f>
+        <v>1.9881199999999999</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="13">
+        <f>AVERAGE(E2:E11)</f>
+        <v>1.9893800000000001</v>
+      </c>
+      <c r="F12" s="14">
+        <f>AVERAGE(F2:F11)</f>
+        <v>1.9902899999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="12">
+        <f>_xlfn.STDEV.S(B2:B11)</f>
+        <v>6.0827625302984929E-4</v>
+      </c>
+      <c r="C13" s="5">
+        <f>_xlfn.STDEV.S(C2:C11)</f>
+        <v>7.554248252914698E-4</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="12">
+        <f>_xlfn.STDEV.S(E2:E11)</f>
+        <v>3.5187750393819938E-3</v>
+      </c>
+      <c r="F13" s="5">
+        <f>_xlfn.STDEV.S(F2:F11)</f>
+        <v>2.9463536787018665E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <f>B13/SQRT(10)</f>
+        <v>1.9235384061672207E-4</v>
+      </c>
+      <c r="C14">
+        <f>C13/SQRT(10)</f>
+        <v>2.3888630489558158E-4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <f>E13/SQRT(10)</f>
+        <v>1.1127343698195788E-3</v>
+      </c>
+      <c r="F14">
+        <f>F13/SQRT(10)</f>
+        <v>9.3171884171138343E-4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -92,7 +92,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="172" formatCode="0.000000000"/>
+    <numFmt numFmtId="165" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -327,7 +327,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">Distanza massa esterna (m)</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t xml:space="preserve">Errore standard della media</t>
-  </si>
-  <si>
-    <t>1,99071,989</t>
   </si>
   <si>
     <t xml:space="preserve">Tempi (s)</t>
@@ -498,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -555,6 +552,9 @@
     <xf fontId="0" fillId="3" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1688,8 +1688,8 @@
       <c r="A15" s="15">
         <v>0.91500000000000004</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>11</v>
+      <c r="B15" s="16">
+        <v>1.9906999999999999</v>
       </c>
       <c r="C15" s="8">
         <v>1.9875</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B25" s="21">
         <f>AVERAGE(B15:B24)</f>
-        <v>1.9911333333333334</v>
+        <v>1.9910900000000002</v>
       </c>
       <c r="C25" s="22">
         <f>AVERAGE(C15:C24)</f>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B26" s="9">
         <f>_xlfn.STDEV.S(B15:B24)</f>
-        <v>6.0827625302984929e-004</v>
+        <v>5.8963265400306707e-004</v>
       </c>
       <c r="C26" s="18">
         <f>_xlfn.STDEV.S(C15:C24)</f>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B27">
         <f>B26/SQRT(10)</f>
-        <v>1.9235384061672207e-004</v>
+        <v>1.8645821694596905e-004</v>
       </c>
       <c r="C27">
         <f>C26/SQRT(10)</f>
@@ -1996,25 +1996,25 @@
     <row r="3">
       <c r="A3" s="28"/>
       <c r="B3" s="35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" s="36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2220,7 +2220,7 @@
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="51">
         <f>_xlfn.STDEV.S(B4:B10)/SQRT(7)</f>
@@ -2294,16 +2294,16 @@
       <c r="A2" s="15">
         <v>0.91500000000000004</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="8">
+      <c r="B2" s="16">
+        <v>1.9906999999999999</v>
+      </c>
+      <c r="C2">
         <v>1.9875</v>
       </c>
       <c r="D2" s="15">
         <v>0.92000000000000004</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2">
         <v>1.9911000000000001</v>
       </c>
       <c r="F2" s="8">
@@ -2315,11 +2315,11 @@
       <c r="B3" s="5">
         <v>1.9911000000000001</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>1.9873000000000001</v>
       </c>
       <c r="D3" s="19"/>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>1.9863</v>
       </c>
       <c r="F3" s="8">
@@ -2331,11 +2331,11 @@
       <c r="B4" s="5">
         <v>1.9908999999999999</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>1.9894000000000001</v>
       </c>
       <c r="D4" s="19"/>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>1.9910000000000001</v>
       </c>
       <c r="F4" s="8">
@@ -2347,11 +2347,11 @@
       <c r="B5" s="5">
         <v>1.9919</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>1.9890000000000001</v>
       </c>
       <c r="D5" s="19"/>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>1.9857</v>
       </c>
       <c r="F5" s="8">
@@ -2363,11 +2363,11 @@
       <c r="B6" s="5">
         <v>1.9908999999999999</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>1.9882</v>
       </c>
       <c r="D6" s="19"/>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>1.9905999999999999</v>
       </c>
       <c r="F6" s="8">
@@ -2379,11 +2379,11 @@
       <c r="B7" s="5">
         <v>1.9906999999999999</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>1.9882</v>
       </c>
       <c r="D7" s="19"/>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>1.9925999999999999</v>
       </c>
       <c r="F7" s="8">
@@ -2395,11 +2395,11 @@
       <c r="B8" s="5">
         <v>1.9913000000000001</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>1.988</v>
       </c>
       <c r="D8" s="19"/>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>1.9928999999999999</v>
       </c>
       <c r="F8" s="8">
@@ -2411,11 +2411,11 @@
       <c r="B9" s="5">
         <v>1.9904999999999999</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>1.9886999999999999</v>
       </c>
       <c r="D9" s="19"/>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>1.9905999999999999</v>
       </c>
       <c r="F9" s="8">
@@ -2427,11 +2427,11 @@
       <c r="B10" s="5">
         <v>1.9905999999999999</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>1.9879</v>
       </c>
       <c r="D10" s="19"/>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>1.982</v>
       </c>
       <c r="F10" s="8">
@@ -2440,17 +2440,17 @@
     </row>
     <row r="11" ht="14.65">
       <c r="A11" s="19"/>
-      <c r="B11" s="5">
+      <c r="B11" s="9">
         <v>1.9923</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="18">
         <v>1.9870000000000001</v>
       </c>
       <c r="D11" s="19"/>
-      <c r="E11" s="5">
+      <c r="E11" s="9">
         <v>1.9910000000000001</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="18">
         <v>1.9839</v>
       </c>
     </row>
@@ -2460,16 +2460,16 @@
       </c>
       <c r="B12" s="21">
         <f>AVERAGE(B2:B11)</f>
-        <v>1.9911333333333334</v>
-      </c>
-      <c r="C12" s="22">
+        <v>1.9910900000000002</v>
+      </c>
+      <c r="C12">
         <f>AVERAGE(C2:C11)</f>
         <v>1.9881199999999999</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="6">
         <f>AVERAGE(E2:E11)</f>
         <v>1.9893800000000001</v>
       </c>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="B13" s="9">
         <f>_xlfn.STDEV.S(B2:B11)</f>
-        <v>6.0827625302984929e-004</v>
+        <v>5.8963265400306707e-004</v>
       </c>
       <c r="C13" s="18">
         <f>_xlfn.STDEV.S(C2:C11)</f>
@@ -2506,22 +2506,22 @@
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="52">
         <f>B13/SQRT(10)</f>
-        <v>1.9235384061672207e-004</v>
-      </c>
-      <c r="C14">
+        <v>1.8645821694596905e-004</v>
+      </c>
+      <c r="C14" s="52">
         <f>C13/SQRT(10)</f>
         <v>2.3888630489558158e-004</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="52">
         <f>E13/SQRT(10)</f>
         <v>1.1127343698195788e-003</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="52">
         <f>F13/SQRT(10)</f>
         <v>9.3171884171138343e-004</v>
       </c>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -64,8 +64,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -495,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -553,6 +554,13 @@
     <xf fontId="0" fillId="3" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -2526,6 +2534,140 @@
         <v>9.3171884171138343e-004</v>
       </c>
     </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="15">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="B16" s="16">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="C16" s="53">
+        <v>1.9874000000000001</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="5">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="C17" s="53">
+        <v>1.988</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="5">
+        <v>1.9904999999999999</v>
+      </c>
+      <c r="C18" s="53">
+        <v>1.9881</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="19"/>
+      <c r="B19" s="5">
+        <v>1.9918</v>
+      </c>
+      <c r="C19" s="53">
+        <v>1.9851000000000001</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="19"/>
+      <c r="B20" s="5">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="C20" s="53">
+        <v>1.9869000000000001</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="19"/>
+      <c r="B21" s="5">
+        <v>1.9914000000000001</v>
+      </c>
+      <c r="C21" s="53">
+        <v>1.9877</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="5">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="C22" s="53">
+        <v>1.9882</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="19"/>
+      <c r="B23" s="5">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="C23" s="53">
+        <v>1.9891000000000001</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="5">
+        <v>1.9907999999999999</v>
+      </c>
+      <c r="C24" s="53">
+        <v>1.9877</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="33"/>
+      <c r="B25" s="9">
+        <v>1.9916</v>
+      </c>
+      <c r="C25" s="18">
+        <v>1.9892000000000001</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="54">
+        <f>AVERAGE(B16:B25)</f>
+        <v>1.9910899999999998</v>
+      </c>
+      <c r="C26" s="55">
+        <f>AVERAGE(C16:C25)</f>
+        <v>1.9877400000000001</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="9">
+        <f>_xlfn.STDEV.S(B16:B25)</f>
+        <v>4.1486276177929101e-004</v>
+      </c>
+      <c r="C27" s="18">
+        <f>_xlfn.STDEV.S(C16:C25)</f>
+        <v>1.1635195648452797e-003</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="52">
+        <f>B27/SQRT(10)</f>
+        <v>1.3119112436104082e-004</v>
+      </c>
+      <c r="C28" s="52">
+        <f>C27/SQRT(10)</f>
+        <v>3.679371927079062e-004</v>
+      </c>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -553,14 +553,14 @@
     <xf fontId="0" fillId="3" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -2271,11 +2271,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="22.265625"/>
-    <col bestFit="1" customWidth="1" min="2" max="3" width="11.73046875"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="22.265625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="13.796875"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="18"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="22.875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="14.125"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="18.79296875"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="22.875"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="14.125"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="18.79296875"/>
+    <col bestFit="1" min="7" max="7" width="22.875"/>
+    <col bestFit="1" min="8" max="8" width="14.125"/>
+    <col bestFit="1" min="9" max="9" width="18.79296875"/>
+    <col bestFit="1" min="10" max="10" width="10.875"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2297,6 +2302,15 @@
       <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="G1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="15">
@@ -2316,6 +2330,15 @@
       </c>
       <c r="F2" s="8">
         <v>1.9866999999999999</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.91800000000000004</v>
+      </c>
+      <c r="H2" s="16">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="I2" s="52">
+        <v>1.9874000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -2333,6 +2356,13 @@
       <c r="F3" s="8">
         <v>1.9923999999999999</v>
       </c>
+      <c r="G3" s="19"/>
+      <c r="H3" s="5">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="I3" s="52">
+        <v>1.988</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="19"/>
@@ -2349,6 +2379,13 @@
       <c r="F4" s="8">
         <v>1.9919</v>
       </c>
+      <c r="G4" s="19"/>
+      <c r="H4" s="5">
+        <v>1.9904999999999999</v>
+      </c>
+      <c r="I4" s="52">
+        <v>1.9881</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="19"/>
@@ -2365,6 +2402,13 @@
       <c r="F5" s="8">
         <v>1.9925999999999999</v>
       </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="5">
+        <v>1.9918</v>
+      </c>
+      <c r="I5" s="52">
+        <v>1.9851000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19"/>
@@ -2381,6 +2425,13 @@
       <c r="F6" s="8">
         <v>1.9903999999999999</v>
       </c>
+      <c r="G6" s="19"/>
+      <c r="H6" s="5">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="I6" s="52">
+        <v>1.9869000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="19"/>
@@ -2397,6 +2448,13 @@
       <c r="F7" s="8">
         <v>1.9904999999999999</v>
       </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="5">
+        <v>1.9914000000000001</v>
+      </c>
+      <c r="I7" s="52">
+        <v>1.9877</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19"/>
@@ -2413,6 +2471,13 @@
       <c r="F8" s="8">
         <v>1.9907999999999999</v>
       </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="5">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="I8" s="52">
+        <v>1.9882</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="19"/>
@@ -2429,6 +2494,13 @@
       <c r="F9" s="8">
         <v>1.9937</v>
       </c>
+      <c r="G9" s="19"/>
+      <c r="H9" s="5">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="I9" s="52">
+        <v>1.9891000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="19"/>
@@ -2445,6 +2517,13 @@
       <c r="F10" s="8">
         <v>1.99</v>
       </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="5">
+        <v>1.9907999999999999</v>
+      </c>
+      <c r="I10" s="52">
+        <v>1.9877</v>
+      </c>
     </row>
     <row r="11" ht="14.65">
       <c r="A11" s="19"/>
@@ -2461,6 +2540,13 @@
       <c r="F11" s="18">
         <v>1.9839</v>
       </c>
+      <c r="G11" s="33"/>
+      <c r="H11" s="9">
+        <v>1.9916</v>
+      </c>
+      <c r="I11" s="18">
+        <v>1.9892000000000001</v>
+      </c>
     </row>
     <row r="12" ht="14.65">
       <c r="A12" s="20" t="s">
@@ -2485,6 +2571,17 @@
         <f>AVERAGE(F2:F11)</f>
         <v>1.9902899999999994</v>
       </c>
+      <c r="G12" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="53">
+        <f>AVERAGE(H2:H11)</f>
+        <v>1.9910899999999998</v>
+      </c>
+      <c r="I12" s="54">
+        <f>AVERAGE(I2:I11)</f>
+        <v>1.9877400000000001</v>
+      </c>
     </row>
     <row r="13" ht="14.65">
       <c r="A13" s="26" t="s">
@@ -2509,164 +2606,57 @@
         <f>_xlfn.STDEV.S(F2:F11)</f>
         <v>2.9463536787018665e-003</v>
       </c>
+      <c r="G13" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="9">
+        <f>_xlfn.STDEV.S(H2:H11)</f>
+        <v>4.1486276177929101e-004</v>
+      </c>
+      <c r="I13" s="18">
+        <f>_xlfn.STDEV.S(I2:I11)</f>
+        <v>1.1635195648452797e-003</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="52">
+      <c r="B14" s="55">
         <f>B13/SQRT(10)</f>
         <v>1.8645821694596905e-004</v>
       </c>
-      <c r="C14" s="52">
+      <c r="C14" s="55">
         <f>C13/SQRT(10)</f>
         <v>2.3888630489558158e-004</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="55">
         <f>E13/SQRT(10)</f>
         <v>1.1127343698195788e-003</v>
       </c>
-      <c r="F14" s="52">
+      <c r="F14" s="55">
         <f>F13/SQRT(10)</f>
         <v>9.3171884171138343e-004</v>
       </c>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="15">
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="B16" s="16">
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="C16" s="53">
-        <v>1.9874000000000001</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="5">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="C17" s="53">
-        <v>1.988</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="5">
-        <v>1.9904999999999999</v>
-      </c>
-      <c r="C18" s="53">
-        <v>1.9881</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="5">
-        <v>1.9918</v>
-      </c>
-      <c r="C19" s="53">
-        <v>1.9851000000000001</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="A20" s="19"/>
-      <c r="B20" s="5">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="C20" s="53">
-        <v>1.9869000000000001</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="A21" s="19"/>
-      <c r="B21" s="5">
-        <v>1.9914000000000001</v>
-      </c>
-      <c r="C21" s="53">
-        <v>1.9877</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="5">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="C22" s="53">
-        <v>1.9882</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="5">
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="C23" s="53">
-        <v>1.9891000000000001</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="5">
-        <v>1.9907999999999999</v>
-      </c>
-      <c r="C24" s="53">
-        <v>1.9877</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="A25" s="33"/>
-      <c r="B25" s="9">
-        <v>1.9916</v>
-      </c>
-      <c r="C25" s="18">
-        <v>1.9892000000000001</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="54">
-        <f>AVERAGE(B16:B25)</f>
-        <v>1.9910899999999998</v>
-      </c>
-      <c r="C26" s="55">
-        <f>AVERAGE(C16:C25)</f>
-        <v>1.9877400000000001</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="A27" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="9">
-        <f>_xlfn.STDEV.S(B16:B25)</f>
-        <v>4.1486276177929101e-004</v>
-      </c>
-      <c r="C27" s="18">
-        <f>_xlfn.STDEV.S(C16:C25)</f>
-        <v>1.1635195648452797e-003</v>
+      <c r="G14" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="55">
+        <f>H13/SQRT(10)</f>
+        <v>1.3119112436104082e-004</v>
+      </c>
+      <c r="I14" s="55">
+        <f>I13/SQRT(10)</f>
+        <v>3.679371927079062e-004</v>
       </c>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="52">
-        <f>B27/SQRT(10)</f>
-        <v>1.3119112436104082e-004</v>
-      </c>
-      <c r="C28" s="52">
-        <f>C27/SQRT(10)</f>
-        <v>3.679371927079062e-004</v>
-      </c>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" state="visible" r:id="rId1"/>
@@ -1692,242 +1692,9 @@
         <v>8.2959829636597285e-004</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15">
-        <v>0.91500000000000004</v>
-      </c>
-      <c r="B15" s="16">
-        <v>1.9906999999999999</v>
-      </c>
-      <c r="C15" s="8">
-        <v>1.9875</v>
-      </c>
-      <c r="D15" s="15">
-        <v>0.92000000000000004</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="F15" s="8">
-        <v>1.9866999999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19"/>
-      <c r="B16" s="5">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="C16" s="8">
-        <v>1.9873000000000001</v>
-      </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="5">
-        <v>1.9863</v>
-      </c>
-      <c r="F16" s="8">
-        <v>1.9923999999999999</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19"/>
-      <c r="B17" s="5">
-        <v>1.9908999999999999</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1.9894000000000001</v>
-      </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="5">
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="F17" s="8">
-        <v>1.9919</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19"/>
-      <c r="B18" s="5">
-        <v>1.9919</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="5">
-        <v>1.9857</v>
-      </c>
-      <c r="F18" s="8">
-        <v>1.9925999999999999</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19"/>
-      <c r="B19" s="5">
-        <v>1.9908999999999999</v>
-      </c>
-      <c r="C19" s="8">
-        <v>1.9882</v>
-      </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="5">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="F19" s="8">
-        <v>1.9903999999999999</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19"/>
-      <c r="B20" s="5">
-        <v>1.9906999999999999</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1.9882</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="5">
-        <v>1.9925999999999999</v>
-      </c>
-      <c r="F20" s="8">
-        <v>1.9904999999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19"/>
-      <c r="B21" s="5">
-        <v>1.9913000000000001</v>
-      </c>
-      <c r="C21" s="8">
-        <v>1.988</v>
-      </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="5">
-        <v>1.9928999999999999</v>
-      </c>
-      <c r="F21" s="8">
-        <v>1.9907999999999999</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19"/>
-      <c r="B22" s="5">
-        <v>1.9904999999999999</v>
-      </c>
-      <c r="C22" s="8">
-        <v>1.9886999999999999</v>
-      </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="5">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="F22" s="8">
-        <v>1.9937</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="19"/>
-      <c r="B23" s="5">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="C23" s="8">
-        <v>1.9879</v>
-      </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="5">
-        <v>1.982</v>
-      </c>
-      <c r="F23" s="8">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="24" ht="14.65">
-      <c r="A24" s="19"/>
-      <c r="B24" s="5">
-        <v>1.9923</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1.9870000000000001</v>
-      </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="5">
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="F24" s="8">
-        <v>1.9839</v>
-      </c>
-    </row>
-    <row r="25" ht="14.65">
-      <c r="A25" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="21">
-        <f>AVERAGE(B15:B24)</f>
-        <v>1.9910900000000002</v>
-      </c>
-      <c r="C25" s="22">
-        <f>AVERAGE(C15:C24)</f>
-        <v>1.9881199999999999</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="24">
-        <f>AVERAGE(E15:E24)</f>
-        <v>1.9893800000000001</v>
-      </c>
-      <c r="F25" s="25">
-        <f>AVERAGE(F15:F24)</f>
-        <v>1.9902899999999994</v>
-      </c>
-    </row>
-    <row r="26" ht="14.65">
-      <c r="A26" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="9">
-        <f>_xlfn.STDEV.S(B15:B24)</f>
-        <v>5.8963265400306707e-004</v>
-      </c>
-      <c r="C26" s="18">
-        <f>_xlfn.STDEV.S(C15:C24)</f>
-        <v>7.554248252914698e-004</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" s="9">
-        <f>_xlfn.STDEV.S(E15:E24)</f>
-        <v>3.5187750393819938e-003</v>
-      </c>
-      <c r="F26" s="18">
-        <f>_xlfn.STDEV.S(F15:F24)</f>
-        <v>2.9463536787018665e-003</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27">
-        <f>B26/SQRT(10)</f>
-        <v>1.8645821694596905e-004</v>
-      </c>
-      <c r="C27">
-        <f>C26/SQRT(10)</f>
-        <v>2.3888630489558158e-004</v>
-      </c>
-      <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27">
-        <f>E26/SQRT(10)</f>
-        <v>1.1127343698195788e-003</v>
-      </c>
-      <c r="F27">
-        <f>F26/SQRT(10)</f>
-        <v>9.3171884171138343e-004</v>
-      </c>
-    </row>
+    <row r="24" ht="14.65"/>
+    <row r="25" ht="14.65"/>
+    <row r="26" ht="14.65"/>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1940,13 +1707,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="10.59765625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="21.46484375"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="10.59765625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="10.59765625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="11.73046875"/>
-    <col customWidth="1" min="7" max="7" width="10.46484375"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="11.73046875"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="15.375"/>
+    <col bestFit="1" customWidth="1" min="2" max="3" width="11.125"/>
+    <col bestFit="1" min="4" max="4" width="11.125"/>
+    <col bestFit="1" customWidth="1" min="5" max="6" width="11.125"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="10.875"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="11.125"/>
     <col bestFit="1" customWidth="1" min="9" max="9" width="10.59765625"/>
     <col bestFit="1" customWidth="1" min="10" max="10" width="11.73046875"/>
     <col bestFit="1" customWidth="1" min="11" max="11" width="10.59765625"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -1,76 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_C700E13B90821D89D5081F7B42FE6E6BA95AC510" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C716C7CE-B24E-4C30-92B5-1E67B90D7F2D}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Periodi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Intersezione" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Caduta libera" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Foglio1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Periodi" sheetId="1" r:id="rId1"/>
+    <sheet name="Intersezione" sheetId="2" r:id="rId2"/>
+    <sheet name="Caduta libera" sheetId="3" r:id="rId3"/>
+    <sheet name="Foglio1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="13">
   <si>
-    <t xml:space="preserve">Distanza massa esterna (m)</t>
+    <t>Distanza massa esterna (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">Distanza massa interna (m)</t>
+    <t>Distanza massa interna (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">T1 (coltello 1) (s)</t>
+    <t>T1 (coltello 1) (s)</t>
   </si>
   <si>
-    <t xml:space="preserve">T2 (massa esterna) (s)</t>
+    <t>T2 (massa esterna) (s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Distanza (m)</t>
+    <t>Distanza (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">h (m)</t>
+    <t>h (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">cateto opposto (m)</t>
+    <t>cateto opposto (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">Errore sulla misura (m)</t>
+    <t>Errore sulla misura (m)</t>
   </si>
   <si>
     <t>Media</t>
   </si>
   <si>
-    <t xml:space="preserve">Deviazione standard</t>
+    <t>Deviazione standard</t>
   </si>
   <si>
-    <t xml:space="preserve">Errore standard della media</t>
+    <t>Errore standard della media</t>
   </si>
   <si>
-    <t xml:space="preserve">Tempi (s)</t>
+    <t>Tempi (s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Errore della media</t>
+    <t>Errore della media</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -96,91 +113,91 @@
   </fills>
   <borders count="33">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -192,8 +209,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -202,9 +219,9 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -219,7 +236,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -228,20 +245,20 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -256,7 +273,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -271,7 +288,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -286,7 +303,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -295,11 +312,11 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -308,11 +325,11 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -327,7 +344,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -342,7 +359,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -354,8 +371,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -367,8 +384,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -377,9 +394,9 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -388,20 +405,20 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -410,11 +427,11 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -423,11 +440,11 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -436,11 +453,11 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -452,19 +469,19 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -476,8 +493,8 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -486,83 +503,78 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
+  <cellXfs count="61">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -580,291 +592,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1075,24 +804,26 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="21.86328125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="22.1328125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="13.796875"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="18"/>
-    <col customWidth="1" min="6" max="6" width="9.06640625"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="22.1328125"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="13.796875"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="18"/>
+    <col min="1" max="1" width="21.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.06640625" customWidth="1"/>
+    <col min="7" max="7" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1106,12 +837,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0.12</v>
       </c>
       <c r="B2" s="5">
-        <v>8.0000000000000002e-002</v>
+        <v>0.08</v>
       </c>
       <c r="C2" s="6">
         <v>1.9995000000000001</v>
@@ -1120,9 +851,9 @@
         <v>1.9543999999999999</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B3" s="5">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="C3" s="6">
         <v>1.9843</v>
@@ -1131,7 +862,7 @@
         <v>1.9044000000000001</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B4" s="5">
         <v>0.13</v>
       </c>
@@ -1142,7 +873,7 @@
         <v>1.8761000000000001</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5" s="5">
         <v>0.16300000000000001</v>
       </c>
@@ -1153,7 +884,7 @@
         <v>1.8714</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B6" s="5">
         <v>0.19</v>
       </c>
@@ -1164,7 +895,7 @@
         <v>1.8234999999999999</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B7" s="5">
         <v>0.22</v>
       </c>
@@ -1175,7 +906,7 @@
         <v>1.8037000000000001</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B8" s="5">
         <v>0.245</v>
       </c>
@@ -1186,9 +917,9 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B9" s="5">
-        <v>0.27000000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="C9" s="6">
         <v>1.9354</v>
@@ -1197,7 +928,7 @@
         <v>1.7618</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B10" s="5">
         <v>0.30499999999999999</v>
       </c>
@@ -1208,7 +939,7 @@
         <v>1.7654000000000001</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B11" s="5">
         <v>0.33700000000000002</v>
       </c>
@@ -1219,7 +950,7 @@
         <v>1.7536</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12" s="5">
         <v>0.379</v>
       </c>
@@ -1230,9 +961,9 @@
         <v>1.7468999999999999</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B13" s="5">
-        <v>0.41999999999999998</v>
+        <v>0.42</v>
       </c>
       <c r="C13" s="6">
         <v>1.9016</v>
@@ -1241,7 +972,7 @@
         <v>1.7565999999999999</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B14" s="5">
         <v>0.46500000000000002</v>
       </c>
@@ -1252,9 +983,9 @@
         <v>1.7608999999999999</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B15" s="5">
-        <v>0.51000000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="C15" s="6">
         <v>1.8929</v>
@@ -1263,20 +994,20 @@
         <v>1.7766</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B16" s="5">
         <v>0.55500000000000005</v>
       </c>
       <c r="C16" s="6">
-        <v>1.8799999999999999</v>
+        <v>1.88</v>
       </c>
       <c r="D16" s="7">
         <v>1.7897000000000001</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" s="5">
-        <v>0.58999999999999997</v>
+        <v>0.59</v>
       </c>
       <c r="C17" s="6">
         <v>1.8823000000000001</v>
@@ -1285,7 +1016,7 @@
         <v>1.8021</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B18" s="5">
         <v>0.622</v>
       </c>
@@ -1296,7 +1027,7 @@
         <v>1.8011999999999999</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B19" s="5">
         <v>0.66300000000000003</v>
       </c>
@@ -1307,7 +1038,7 @@
         <v>1.8382000000000001</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" s="5">
         <v>0.70499999999999996</v>
       </c>
@@ -1318,9 +1049,9 @@
         <v>1.8492999999999999</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" s="5">
-        <v>0.73999999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="C21" s="6">
         <v>1.9069</v>
@@ -1329,7 +1060,7 @@
         <v>1.8694</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" s="5">
         <v>0.77500000000000002</v>
       </c>
@@ -1340,9 +1071,9 @@
         <v>1.8993</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B23" s="5">
-        <v>0.81000000000000005</v>
+        <v>0.81</v>
       </c>
       <c r="C23" s="6">
         <v>1.9296</v>
@@ -1351,7 +1082,7 @@
         <v>1.9175</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" s="5">
         <v>0.83799999999999997</v>
       </c>
@@ -1362,7 +1093,7 @@
         <v>1.9319</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B25" s="5">
         <v>0.88200000000000001</v>
       </c>
@@ -1373,7 +1104,7 @@
         <v>1.9626999999999999</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B26" s="5">
         <v>0.91500000000000004</v>
       </c>
@@ -1384,9 +1115,9 @@
         <v>1.9879</v>
       </c>
     </row>
-    <row r="27" ht="14.65">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B27" s="9">
-        <v>0.92000000000000004</v>
+        <v>0.92</v>
       </c>
       <c r="C27" s="10">
         <v>1.9931000000000001</v>
@@ -1396,29 +1127,28 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="22.1328125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="13.796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="18"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="16.59765625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="13.796875"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="18"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="5.73046875"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="15.6640625"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="18.46484375"/>
+    <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>1</v>
       </c>
@@ -1447,7 +1177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="14.65">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="15">
         <v>0.91500000000000004</v>
       </c>
@@ -1458,7 +1188,7 @@
         <v>1.9834000000000001</v>
       </c>
       <c r="D2" s="15">
-        <v>0.92000000000000004</v>
+        <v>0.92</v>
       </c>
       <c r="E2" s="5">
         <v>1.9897</v>
@@ -1470,13 +1200,13 @@
         <v>1.0049999999999999</v>
       </c>
       <c r="H2" s="17">
-        <v>8.9999999999999997e-002</v>
-      </c>
-      <c r="I2" s="18">
-        <v>5.0000000000000001e-003</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>0.09</v>
+      </c>
+      <c r="I2" s="55">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="19"/>
       <c r="B3" s="5">
         <v>1.9903999999999999</v>
@@ -1492,7 +1222,7 @@
         <v>1.9921</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="19"/>
       <c r="B4" s="5">
         <v>1.9878</v>
@@ -1508,7 +1238,7 @@
         <v>1.9892000000000001</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="19"/>
       <c r="B5" s="5">
         <v>1.9887999999999999</v>
@@ -1524,7 +1254,7 @@
         <v>1.9832000000000001</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="19"/>
       <c r="B6" s="5">
         <v>1.9905999999999999</v>
@@ -1540,12 +1270,12 @@
         <v>1.9914000000000001</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="19"/>
       <c r="B7" s="5">
         <v>1.9893000000000001</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="54">
         <v>1.99</v>
       </c>
       <c r="D7" s="19"/>
@@ -1556,7 +1286,7 @@
         <v>1.9901</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="19"/>
       <c r="B8" s="5">
         <v>1.9886999999999999</v>
@@ -1565,14 +1295,14 @@
         <v>1.9866999999999999</v>
       </c>
       <c r="D8" s="19"/>
-      <c r="E8" s="5">
+      <c r="E8" s="53">
         <v>1.99</v>
       </c>
       <c r="F8" s="8">
         <v>1.9899</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="19"/>
       <c r="B9" s="5">
         <v>1.9869000000000001</v>
@@ -1588,7 +1318,7 @@
         <v>1.9891000000000001</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="19"/>
       <c r="B10" s="5">
         <v>1.9886999999999999</v>
@@ -1604,7 +1334,7 @@
         <v>1.9921</v>
       </c>
     </row>
-    <row r="11" ht="14.65">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="19"/>
       <c r="B11" s="5">
         <v>1.9873000000000001</v>
@@ -1620,204 +1350,197 @@
         <v>1.9881</v>
       </c>
     </row>
-    <row r="12" ht="14.65">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="23">
         <f>AVERAGE(B2:B11)</f>
         <v>1.9887500000000002</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="21">
         <f>AVERAGE(C2:C11)</f>
         <v>1.9864999999999999</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="23">
         <f>AVERAGE(E2:E11)</f>
         <v>1.9890900000000002</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="24">
         <f>AVERAGE(F2:F11)</f>
         <v>1.98963</v>
       </c>
     </row>
-    <row r="13" ht="14.65">
-      <c r="A13" s="26" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="52">
         <f>_xlfn.STDEV.S(B2:B11)</f>
-        <v>1.1993053545003578e-003</v>
-      </c>
-      <c r="C13" s="18">
+        <v>1.1993053545003578E-3</v>
+      </c>
+      <c r="C13" s="11">
         <f>_xlfn.STDEV.S(C2:C11)</f>
-        <v>2.0965580258021552e-003</v>
-      </c>
-      <c r="D13" s="27" t="s">
+        <v>2.0965580258021552E-3</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="52">
         <f>_xlfn.STDEV.S(E2:E11)</f>
-        <v>2.0512597755200563e-003</v>
-      </c>
-      <c r="F13" s="18">
+        <v>2.0512597755200563E-3</v>
+      </c>
+      <c r="F13" s="11">
         <f>_xlfn.STDEV.S(F2:F11)</f>
-        <v>2.6234201595118625e-003</v>
-      </c>
-    </row>
-    <row r="14" ht="14.65">
+        <v>2.6234201595118625E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="10">
         <f>B13/SQRT(10)</f>
-        <v>3.7925365302567999e-004</v>
-      </c>
-      <c r="C14" s="17">
+        <v>3.7925365302567999E-4</v>
+      </c>
+      <c r="C14" s="10">
         <f>C13/SQRT(10)</f>
-        <v>6.6298986082408758e-004</v>
-      </c>
-      <c r="D14" s="17" t="s">
+        <v>6.6298986082408758E-4</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="10">
         <f>E13/SQRT(10)</f>
-        <v>6.4866529633290785e-004</v>
-      </c>
-      <c r="F14" s="18">
+        <v>6.4866529633290785E-4</v>
+      </c>
+      <c r="F14" s="11">
         <f>F13/SQRT(10)</f>
-        <v>8.2959829636597285e-004</v>
-      </c>
-    </row>
-    <row r="24" ht="14.65"/>
-    <row r="25" ht="14.65"/>
-    <row r="26" ht="14.65"/>
+        <v>8.2959829636597285E-4</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="15.375"/>
-    <col bestFit="1" customWidth="1" min="2" max="3" width="11.125"/>
-    <col bestFit="1" min="4" max="4" width="11.125"/>
-    <col bestFit="1" customWidth="1" min="5" max="6" width="11.125"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="10.875"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="11.125"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="10.59765625"/>
-    <col bestFit="1" customWidth="1" min="10" max="10" width="11.73046875"/>
-    <col bestFit="1" customWidth="1" min="11" max="11" width="10.59765625"/>
-    <col bestFit="1" customWidth="1" min="12" max="12" width="7.9296875"/>
+    <col min="1" max="1" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.65">
-      <c r="A1" s="28"/>
-      <c r="B1" s="29" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" s="27"/>
+      <c r="B1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="28"/>
-      <c r="B2" s="32">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="C2" s="33">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="D2" s="33">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="27"/>
+      <c r="B2" s="31">
+        <v>0.15</v>
+      </c>
+      <c r="C2" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="32">
         <v>0.25</v>
       </c>
-      <c r="E2" s="33">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="F2" s="33">
-        <v>0.34999999999999998</v>
-      </c>
-      <c r="G2" s="33">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="H2" s="34">
-        <v>0.45000000000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="35" t="s">
+      <c r="E2" s="32">
+        <v>0.3</v>
+      </c>
+      <c r="F2" s="32">
+        <v>0.35</v>
+      </c>
+      <c r="G2" s="32">
+        <v>0.4</v>
+      </c>
+      <c r="H2" s="33">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" s="27"/>
+      <c r="B3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="36" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="28"/>
-      <c r="B4" s="38">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="27"/>
+      <c r="B4" s="37">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="38">
         <v>0.16980000000000001</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="38">
         <v>0.19339999999999999</v>
       </c>
-      <c r="E4" s="39">
+      <c r="E4" s="38">
         <v>0.21460000000000001</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="38">
         <v>0.23419999999999999</v>
       </c>
-      <c r="G4" s="39">
+      <c r="G4" s="38">
         <v>0.25280000000000002</v>
       </c>
-      <c r="H4" s="40">
+      <c r="H4" s="39">
         <v>0.27129999999999999</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="28"/>
-      <c r="B5" s="41">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="27"/>
+      <c r="B5" s="40">
         <v>0.1434</v>
       </c>
       <c r="C5" s="19">
@@ -1835,13 +1558,13 @@
       <c r="G5" s="19">
         <v>0.253</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="41">
         <v>0.27189999999999998</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="28"/>
-      <c r="B6" s="41">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="27"/>
+      <c r="B6" s="40">
         <v>0.14330000000000001</v>
       </c>
       <c r="C6" s="19">
@@ -1859,13 +1582,13 @@
       <c r="G6" s="19">
         <v>0.25369999999999998</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="41">
         <v>0.27210000000000001</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="28"/>
-      <c r="B7" s="41">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="27"/>
+      <c r="B7" s="40">
         <v>0.1431</v>
       </c>
       <c r="C7" s="19">
@@ -1883,13 +1606,13 @@
       <c r="G7" s="19">
         <v>0.25319999999999998</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="41">
         <v>0.27079999999999999</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="28"/>
-      <c r="B8" s="41">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="27"/>
+      <c r="B8" s="40">
         <v>0.14319999999999999</v>
       </c>
       <c r="C8" s="19">
@@ -1907,13 +1630,13 @@
       <c r="G8" s="19">
         <v>0.25359999999999999</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="41">
         <v>0.27179999999999999</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="28"/>
-      <c r="B9" s="41">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="27"/>
+      <c r="B9" s="40">
         <v>0.14330000000000001</v>
       </c>
       <c r="C9" s="19">
@@ -1931,125 +1654,124 @@
       <c r="G9" s="19">
         <v>0.253</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="41">
         <v>0.26860000000000001</v>
       </c>
     </row>
-    <row r="10" ht="14.65">
-      <c r="A10" s="43"/>
-      <c r="B10" s="44">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="42"/>
+      <c r="B10" s="43">
         <v>0.1431</v>
       </c>
-      <c r="C10" s="45">
-        <v>0.17000000000000001</v>
-      </c>
-      <c r="D10" s="45">
+      <c r="C10" s="44">
+        <v>0.17</v>
+      </c>
+      <c r="D10" s="44">
         <v>0.19359999999999999</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="44">
         <v>0.21479999999999999</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="44">
         <v>0.23430000000000001</v>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="44">
         <v>0.25340000000000001</v>
       </c>
-      <c r="H10" s="46">
+      <c r="H10" s="45">
         <v>0.26829999999999998</v>
       </c>
     </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="47" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="46" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="48">
-        <f>AVERAGE(B4:B10)</f>
+        <f t="shared" ref="B11:H11" si="0">AVERAGE(B4:B10)</f>
         <v>0.14324285714285714</v>
       </c>
-      <c r="C11" s="49">
-        <f>AVERAGE(C4:C10)</f>
+      <c r="C11" s="51">
+        <f t="shared" si="0"/>
         <v>0.17062857142857141</v>
       </c>
-      <c r="D11" s="49">
-        <f>AVERAGE(D4:D10)</f>
+      <c r="D11" s="51">
+        <f t="shared" si="0"/>
         <v>0.19338571428571427</v>
       </c>
-      <c r="E11" s="49">
-        <f>AVERAGE(E4:E10)</f>
+      <c r="E11" s="51">
+        <f t="shared" si="0"/>
         <v>0.21485714285714286</v>
       </c>
-      <c r="F11" s="49">
-        <f>AVERAGE(F4:F10)</f>
+      <c r="F11" s="51">
+        <f t="shared" si="0"/>
         <v>0.23432857142857141</v>
       </c>
-      <c r="G11" s="49">
-        <f>AVERAGE(G4:G10)</f>
+      <c r="G11" s="51">
+        <f t="shared" si="0"/>
         <v>0.25324285714285721</v>
       </c>
-      <c r="H11" s="49">
-        <f>AVERAGE(H4:H10)</f>
+      <c r="H11" s="51">
+        <f t="shared" si="0"/>
         <v>0.27068571428571425</v>
       </c>
     </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="50" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="51">
-        <f>_xlfn.STDEV.S(B4:B10)/SQRT(7)</f>
-        <v>4.2857142857143202e-005</v>
-      </c>
-      <c r="C12" s="26">
-        <f>_xlfn.STDEV.S(C4:C10)/SQRT(7)</f>
-        <v>2.4369603013188476e-004</v>
-      </c>
-      <c r="D12" s="26">
-        <f>_xlfn.STDEV.S(D4:D10)/SQRT(7)</f>
-        <v>5.9476171413316292e-005</v>
-      </c>
-      <c r="E12" s="26">
-        <f>_xlfn.STDEV.S(E4:E10)/SQRT(7)</f>
-        <v>7.514158970504462e-005</v>
-      </c>
-      <c r="F12" s="26">
-        <f>_xlfn.STDEV.S(F4:F10)/SQRT(7)</f>
-        <v>4.2056004125370102e-005</v>
-      </c>
-      <c r="G12" s="26">
-        <f>_xlfn.STDEV.S(G4:G10)/SQRT(7)</f>
-        <v>1.2697420596164739e-004</v>
-      </c>
-      <c r="H12" s="26">
-        <f>_xlfn.STDEV.S(H4:H10)/SQRT(7)</f>
-        <v>6.0056662586997192e-004</v>
+      <c r="B12" s="49">
+        <f t="shared" ref="B12:H12" si="1">_xlfn.STDEV.S(B4:B10)/SQRT(7)</f>
+        <v>4.2857142857143202E-5</v>
+      </c>
+      <c r="C12" s="50">
+        <f t="shared" si="1"/>
+        <v>2.4369603013188476E-4</v>
+      </c>
+      <c r="D12" s="50">
+        <f t="shared" si="1"/>
+        <v>5.9476171413316292E-5</v>
+      </c>
+      <c r="E12" s="50">
+        <f t="shared" si="1"/>
+        <v>7.514158970504462E-5</v>
+      </c>
+      <c r="F12" s="50">
+        <f t="shared" si="1"/>
+        <v>4.2056004125370102E-5</v>
+      </c>
+      <c r="G12" s="50">
+        <f t="shared" si="1"/>
+        <v>1.2697420596164739E-4</v>
+      </c>
+      <c r="H12" s="50">
+        <f t="shared" si="1"/>
+        <v>6.0056662586997192E-4</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="22.875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="14.125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="18.79296875"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="22.875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="14.125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="18.79296875"/>
-    <col bestFit="1" min="7" max="7" width="22.875"/>
-    <col bestFit="1" min="8" max="8" width="14.125"/>
-    <col bestFit="1" min="9" max="9" width="18.79296875"/>
-    <col bestFit="1" min="10" max="10" width="10.875"/>
+    <col min="1" max="1" width="22.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.86328125" bestFit="1"/>
+    <col min="8" max="8" width="14.1328125" bestFit="1"/>
+    <col min="9" max="9" width="18.796875" bestFit="1"/>
+    <col min="10" max="10" width="10.86328125" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>1</v>
       </c>
@@ -2078,23 +1800,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="15">
         <v>0.91500000000000004</v>
       </c>
       <c r="B2" s="16">
         <v>1.9906999999999999</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6">
         <v>1.9875</v>
       </c>
-      <c r="D2" s="15">
-        <v>0.92000000000000004</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="60">
+        <v>0.92</v>
+      </c>
+      <c r="E2" s="6">
         <v>1.9911000000000001</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>1.9866999999999999</v>
       </c>
       <c r="G2" s="15">
@@ -2103,210 +1825,210 @@
       <c r="H2" s="16">
         <v>1.9910000000000001</v>
       </c>
-      <c r="I2" s="52">
+      <c r="I2" s="8">
         <v>1.9874000000000001</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="19"/>
       <c r="B3" s="5">
         <v>1.9911000000000001</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6">
         <v>1.9873000000000001</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3">
+      <c r="D3" s="59"/>
+      <c r="E3" s="6">
         <v>1.9863</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>1.9923999999999999</v>
       </c>
       <c r="G3" s="19"/>
       <c r="H3" s="5">
         <v>1.9911000000000001</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="7">
         <v>1.988</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="19"/>
       <c r="B4" s="5">
         <v>1.9908999999999999</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="6">
         <v>1.9894000000000001</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4">
+      <c r="D4" s="59"/>
+      <c r="E4" s="6">
         <v>1.9910000000000001</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>1.9919</v>
       </c>
       <c r="G4" s="19"/>
       <c r="H4" s="5">
         <v>1.9904999999999999</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="8">
         <v>1.9881</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="19"/>
       <c r="B5" s="5">
         <v>1.9919</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="6">
         <v>1.9890000000000001</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5">
+      <c r="D5" s="59"/>
+      <c r="E5" s="6">
         <v>1.9857</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>1.9925999999999999</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="5">
         <v>1.9918</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="8">
         <v>1.9851000000000001</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="19"/>
       <c r="B6" s="5">
         <v>1.9908999999999999</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>1.9882</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6">
+      <c r="D6" s="59"/>
+      <c r="E6" s="6">
         <v>1.9905999999999999</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>1.9903999999999999</v>
       </c>
       <c r="G6" s="19"/>
       <c r="H6" s="5">
         <v>1.9911000000000001</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="8">
         <v>1.9869000000000001</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="19"/>
       <c r="B7" s="5">
         <v>1.9906999999999999</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="6">
         <v>1.9882</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7">
+      <c r="D7" s="59"/>
+      <c r="E7" s="6">
         <v>1.9925999999999999</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>1.9904999999999999</v>
       </c>
       <c r="G7" s="19"/>
       <c r="H7" s="5">
         <v>1.9914000000000001</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="8">
         <v>1.9877</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="19"/>
       <c r="B8" s="5">
         <v>1.9913000000000001</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="6">
         <v>1.988</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8">
+      <c r="D8" s="59"/>
+      <c r="E8" s="6">
         <v>1.9928999999999999</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>1.9907999999999999</v>
       </c>
       <c r="G8" s="19"/>
       <c r="H8" s="5">
         <v>1.9905999999999999</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="8">
         <v>1.9882</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="19"/>
       <c r="B9" s="5">
         <v>1.9904999999999999</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="6">
         <v>1.9886999999999999</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9">
+      <c r="D9" s="59"/>
+      <c r="E9" s="6">
         <v>1.9905999999999999</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>1.9937</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="5">
+      <c r="G9" s="59"/>
+      <c r="H9" s="16">
         <v>1.9910000000000001</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="8">
         <v>1.9891000000000001</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="19"/>
       <c r="B10" s="5">
         <v>1.9905999999999999</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="6">
         <v>1.9879</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10">
+      <c r="D10" s="59"/>
+      <c r="E10" s="6">
         <v>1.982</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>1.99</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="5">
+      <c r="G10" s="59"/>
+      <c r="H10" s="16">
         <v>1.9907999999999999</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="8">
         <v>1.9877</v>
       </c>
     </row>
-    <row r="11" ht="14.65">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="19"/>
       <c r="B11" s="9">
         <v>1.9923</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="11">
         <v>1.9870000000000001</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="9">
+      <c r="D11" s="59"/>
+      <c r="E11" s="52">
         <v>1.9910000000000001</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="11">
         <v>1.9839</v>
       </c>
-      <c r="G11" s="33"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="9">
         <v>1.9916</v>
       </c>
@@ -2314,120 +2036,113 @@
         <v>1.9892000000000001</v>
       </c>
     </row>
-    <row r="12" ht="14.65">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="23">
         <f>AVERAGE(B2:B11)</f>
         <v>1.9910900000000002</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="6">
         <f>AVERAGE(C2:C11)</f>
         <v>1.9881199999999999</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="56" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="6">
         <f>AVERAGE(E2:E11)</f>
         <v>1.9893800000000001</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="24">
         <f>AVERAGE(F2:F11)</f>
         <v>1.9902899999999994</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="53">
+      <c r="H12" s="23">
         <f>AVERAGE(H2:H11)</f>
         <v>1.9910899999999998</v>
       </c>
-      <c r="I12" s="54">
+      <c r="I12" s="24">
         <f>AVERAGE(I2:I11)</f>
         <v>1.9877400000000001</v>
       </c>
     </row>
-    <row r="13" ht="14.65">
-      <c r="A13" s="26" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="52">
         <f>_xlfn.STDEV.S(B2:B11)</f>
-        <v>5.8963265400306707e-004</v>
-      </c>
-      <c r="C13" s="18">
+        <v>5.8963265400306707E-4</v>
+      </c>
+      <c r="C13" s="11">
         <f>_xlfn.STDEV.S(C2:C11)</f>
-        <v>7.554248252914698e-004</v>
-      </c>
-      <c r="D13" s="27" t="s">
+        <v>7.554248252914698E-4</v>
+      </c>
+      <c r="D13" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="52">
         <f>_xlfn.STDEV.S(E2:E11)</f>
-        <v>3.5187750393819938e-003</v>
-      </c>
-      <c r="F13" s="18">
+        <v>3.5187750393819938E-3</v>
+      </c>
+      <c r="F13" s="11">
         <f>_xlfn.STDEV.S(F2:F11)</f>
-        <v>2.9463536787018665e-003</v>
-      </c>
-      <c r="G13" s="26" t="s">
+        <v>2.9463536787018665E-3</v>
+      </c>
+      <c r="G13" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="52">
         <f>_xlfn.STDEV.S(H2:H11)</f>
-        <v>4.1486276177929101e-004</v>
-      </c>
-      <c r="I13" s="18">
+        <v>4.1486276177929101E-4</v>
+      </c>
+      <c r="I13" s="11">
         <f>_xlfn.STDEV.S(I2:I11)</f>
-        <v>1.1635195648452797e-003</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>1.1635195648452797E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="55">
+      <c r="B14" s="6">
         <f>B13/SQRT(10)</f>
-        <v>1.8645821694596905e-004</v>
-      </c>
-      <c r="C14" s="55">
+        <v>1.8645821694596905E-4</v>
+      </c>
+      <c r="C14" s="6">
         <f>C13/SQRT(10)</f>
-        <v>2.3888630489558158e-004</v>
-      </c>
-      <c r="D14" t="s">
+        <v>2.3888630489558158E-4</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="6">
         <f>E13/SQRT(10)</f>
-        <v>1.1127343698195788e-003</v>
-      </c>
-      <c r="F14" s="55">
+        <v>1.1127343698195788E-3</v>
+      </c>
+      <c r="F14" s="6">
         <f>F13/SQRT(10)</f>
-        <v>9.3171884171138343e-004</v>
-      </c>
-      <c r="G14" s="55" t="s">
+        <v>9.3171884171138343E-4</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="55">
+      <c r="H14" s="6">
         <f>H13/SQRT(10)</f>
-        <v>1.3119112436104082e-004</v>
-      </c>
-      <c r="I14" s="55">
+        <v>1.3119112436104082E-4</v>
+      </c>
+      <c r="I14" s="6">
         <f>I13/SQRT(10)</f>
-        <v>3.679371927079062e-004</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25">
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
+        <v>3.679371927079062E-4</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,21 +18,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t xml:space="preserve">Distanza massa esterna (m)</t>
+    <t xml:space="preserve">D m.e. [m]</t>
   </si>
   <si>
-    <t xml:space="preserve">Distanza massa interna (m)</t>
+    <t xml:space="preserve">D m.i. [m]</t>
   </si>
   <si>
-    <t xml:space="preserve">T1 (coltello 1) (s)</t>
+    <t xml:space="preserve">T1 [s]</t>
   </si>
   <si>
-    <t xml:space="preserve">T2 (massa esterna) (s)</t>
+    <t xml:space="preserve">T2 [s]</t>
   </si>
   <si>
-    <t xml:space="preserve">Distanza (m)</t>
+    <t xml:space="preserve">Distanza m. interna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,915 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,920 m</t>
   </si>
   <si>
     <t>Media</t>
@@ -41,10 +47,13 @@
     <t xml:space="preserve">Deviazione standard</t>
   </si>
   <si>
-    <t xml:space="preserve">Errore standard della media</t>
+    <t xml:space="preserve">Err. media</t>
   </si>
   <si>
-    <t xml:space="preserve">Tempi (s)</t>
+    <t xml:space="preserve">Distanza [m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempi [s]</t>
   </si>
   <si>
     <t xml:space="preserve">Errore della media</t>
@@ -54,8 +63,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -65,7 +75,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -74,22 +84,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="5"/>
+        <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor theme="3" tint="0.249977111117893"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="0"/>
-        <bgColor theme="0" tint="0"/>
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor theme="3" tint="0.499984740745262"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="39">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -99,20 +105,107 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
       <right style="none"/>
       <top style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </top>
-      <bottom style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="none"/>
       <top style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -122,6 +215,15 @@
       <right style="medium">
         <color auto="1"/>
       </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -129,8 +231,28 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
@@ -139,11 +261,99 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="none"/>
-      <bottom style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -158,31 +368,48 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
       <right style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
@@ -197,133 +424,10 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -334,30 +438,15 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="none"/>
@@ -365,27 +454,10 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
+        <color auto="1"/>
       </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
+      <right style="none"/>
       <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -422,19 +494,6 @@
         <color theme="1"/>
       </top>
       <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -476,61 +535,99 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="66">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="17" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="24" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="25" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="26" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="27" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="22" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="29" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="31" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="23" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="25" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="34" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="35" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="36" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="37" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="38" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1050,10 +1147,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="21.86328125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="22.1328125"/>
+    <col customWidth="1" min="1" max="1" width="9.75390625"/>
+    <col customWidth="1" min="2" max="2" width="10.25390625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="13.796875"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="18"/>
+    <col customWidth="1" min="4" max="4" width="13.125"/>
     <col customWidth="1" min="6" max="6" width="9.06640625"/>
     <col bestFit="1" customWidth="1" min="7" max="7" width="22.1328125"/>
     <col bestFit="1" customWidth="1" min="8" max="8" width="13.796875"/>
@@ -1070,12 +1167,12 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" s="4">
         <v>0.12</v>
       </c>
       <c r="B2" s="5">
@@ -1348,18 +1445,18 @@
       <c r="C26">
         <v>1.9802999999999999</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="5">
         <v>1.9879</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="9">
+      <c r="B27" s="8">
         <v>0.92000000000000004</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>1.9931000000000001</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <v>1.9933000000000001</v>
       </c>
     </row>
@@ -1376,10 +1473,10 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="22.86328125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="14.1328125"/>
+    <col customWidth="1" min="2" max="2" width="18.00390625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="18.796875"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="22.86328125"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="14.1328125"/>
+    <col customWidth="1" min="5" max="5" width="17.625"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="18.796875"/>
     <col bestFit="1" min="7" max="7" width="22.86328125"/>
     <col bestFit="1" min="8" max="8" width="14.1328125"/>
@@ -1388,376 +1485,265 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="E1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13">
-        <v>0.91500000000000004</v>
-      </c>
-      <c r="B2" s="14">
+    </row>
+    <row r="3">
+      <c r="B3" s="18">
         <v>1.9906999999999999</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C3" s="18">
         <v>1.9875</v>
       </c>
-      <c r="D2" s="15">
-        <v>0.92000000000000004</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="E3" s="18">
         <v>1.9911000000000001</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F3" s="19">
         <v>1.9866999999999999</v>
       </c>
-      <c r="G2" s="13">
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="H2" s="14">
+    </row>
+    <row r="4">
+      <c r="B4" s="5">
+        <v>1.9911000000000001</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1.9873000000000001</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7">
+        <v>1.9863</v>
+      </c>
+      <c r="F4" s="20">
+        <v>1.9923999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21"/>
+      <c r="B5" s="5">
+        <v>1.9908999999999999</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1.9894000000000001</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="7">
         <v>1.9910000000000001</v>
       </c>
-      <c r="I2" s="8">
-        <v>1.9874000000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="5">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="C3" s="6">
-        <v>1.9873000000000001</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="6">
-        <v>1.9863</v>
-      </c>
-      <c r="F3" s="7">
-        <v>1.9923999999999999</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="5">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="I3" s="7">
+      <c r="F5" s="20">
+        <v>1.9919</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21"/>
+      <c r="B6" s="5">
+        <v>1.9919</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.9890000000000001</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7">
+        <v>1.9857</v>
+      </c>
+      <c r="F6" s="20">
+        <v>1.9925999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21"/>
+      <c r="B7" s="5">
+        <v>1.9908999999999999</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1.9882</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F7" s="20">
+        <v>1.9903999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21"/>
+      <c r="B8" s="5">
+        <v>1.9906999999999999</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1.9882</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7">
+        <v>1.9925999999999999</v>
+      </c>
+      <c r="F8" s="20">
+        <v>1.9904999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21"/>
+      <c r="B9" s="5">
+        <v>1.9913000000000001</v>
+      </c>
+      <c r="C9" s="7">
         <v>1.988</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16"/>
-      <c r="B4" s="5">
-        <v>1.9908999999999999</v>
-      </c>
-      <c r="C4" s="6">
-        <v>1.9894000000000001</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="6">
+      <c r="D9" s="6"/>
+      <c r="E9" s="7">
+        <v>1.9928999999999999</v>
+      </c>
+      <c r="F9" s="20">
+        <v>1.9907999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21"/>
+      <c r="B10" s="5">
+        <v>1.9904999999999999</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1.9886999999999999</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="F10" s="20">
+        <v>1.9937</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21"/>
+      <c r="B11" s="5">
+        <v>1.9905999999999999</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1.9879</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7">
+        <v>1.982</v>
+      </c>
+      <c r="F11" s="20">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21"/>
+      <c r="B12" s="5">
+        <v>1.9923</v>
+      </c>
+      <c r="C12" s="10">
+        <v>1.9870000000000001</v>
+      </c>
+      <c r="E12" s="7">
         <v>1.9910000000000001</v>
       </c>
-      <c r="F4" s="7">
-        <v>1.9919</v>
-      </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="5">
-        <v>1.9904999999999999</v>
-      </c>
-      <c r="I4" s="8">
-        <v>1.9881</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16"/>
-      <c r="B5" s="5">
-        <v>1.9919</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="6">
-        <v>1.9857</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1.9925999999999999</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="5">
-        <v>1.9918</v>
-      </c>
-      <c r="I5" s="8">
-        <v>1.9851000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16"/>
-      <c r="B6" s="5">
-        <v>1.9908999999999999</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1.9882</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="6">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1.9903999999999999</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="5">
-        <v>1.9911000000000001</v>
-      </c>
-      <c r="I6" s="8">
-        <v>1.9869000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16"/>
-      <c r="B7" s="5">
-        <v>1.9906999999999999</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1.9882</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="6">
-        <v>1.9925999999999999</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1.9904999999999999</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="5">
-        <v>1.9914000000000001</v>
-      </c>
-      <c r="I7" s="8">
-        <v>1.9877</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16"/>
-      <c r="B8" s="5">
-        <v>1.9913000000000001</v>
-      </c>
-      <c r="C8" s="6">
-        <v>1.988</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="6">
-        <v>1.9928999999999999</v>
-      </c>
-      <c r="F8" s="7">
-        <v>1.9907999999999999</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="5">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1.9882</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16"/>
-      <c r="B9" s="5">
-        <v>1.9904999999999999</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1.9886999999999999</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="6">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1.9937</v>
-      </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="14">
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="I9" s="8">
-        <v>1.9891000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16"/>
-      <c r="B10" s="5">
-        <v>1.9905999999999999</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1.9879</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="6">
-        <v>1.982</v>
-      </c>
-      <c r="F10" s="7">
-        <v>1.99</v>
-      </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="14">
-        <v>1.9907999999999999</v>
-      </c>
-      <c r="I10" s="8">
-        <v>1.9877</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16"/>
-      <c r="B11" s="9">
-        <v>1.9923</v>
-      </c>
-      <c r="C11" s="11">
-        <v>1.9870000000000001</v>
-      </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18">
-        <v>1.9910000000000001</v>
-      </c>
-      <c r="F11" s="11">
+      <c r="F12" s="20">
         <v>1.9839</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="9">
-        <v>1.9916</v>
-      </c>
-      <c r="I11" s="20">
-        <v>1.9892000000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="22">
-        <f>AVERAGE(B2:B11)</f>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="23">
+        <f>AVERAGE(B3:B12)</f>
         <v>1.9910900000000002</v>
       </c>
-      <c r="C12" s="6">
-        <f>AVERAGE(C2:C11)</f>
+      <c r="C13" s="24">
+        <f>AVERAGE(C3:C12)</f>
         <v>1.9881199999999999</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="6">
-        <f>AVERAGE(E2:E11)</f>
+      <c r="D13" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="23">
+        <f>AVERAGE(E3:E12)</f>
         <v>1.9893800000000001</v>
       </c>
-      <c r="F12" s="24">
-        <f>AVERAGE(F2:F11)</f>
+      <c r="F13" s="26">
+        <f>AVERAGE(F3:F12)</f>
         <v>1.9902899999999994</v>
       </c>
-      <c r="G12" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="22">
-        <f>AVERAGE(H2:H11)</f>
-        <v>1.9910899999999998</v>
-      </c>
-      <c r="I12" s="24">
-        <f>AVERAGE(I2:I11)</f>
-        <v>1.9877400000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="18">
-        <f>_xlfn.STDEV.S(B2:B11)</f>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="28">
+        <f>_xlfn.STDEV.S(B3:B12)</f>
         <v>5.8963265400306707e-004</v>
       </c>
-      <c r="C13" s="11">
-        <f>_xlfn.STDEV.S(C2:C11)</f>
+      <c r="C14" s="29">
+        <f>_xlfn.STDEV.S(C3:C12)</f>
         <v>7.554248252914698e-004</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="18">
-        <f>_xlfn.STDEV.S(E2:E11)</f>
+      <c r="D14" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="28">
+        <f>_xlfn.STDEV.S(E3:E12)</f>
         <v>3.5187750393819938e-003</v>
       </c>
-      <c r="F13" s="11">
-        <f>_xlfn.STDEV.S(F2:F11)</f>
+      <c r="F14" s="31">
+        <f>_xlfn.STDEV.S(F3:F12)</f>
         <v>2.9463536787018665e-003</v>
       </c>
-      <c r="G13" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="18">
-        <f>_xlfn.STDEV.S(H2:H11)</f>
-        <v>4.1486276177929101e-004</v>
-      </c>
-      <c r="I13" s="11">
-        <f>_xlfn.STDEV.S(I2:I11)</f>
-        <v>1.1635195648452797e-003</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="6">
-        <f>B13/SQRT(10)</f>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="33">
+        <f>B14/SQRT(10)</f>
         <v>1.8645821694596905e-004</v>
       </c>
-      <c r="C14" s="6">
-        <f>C13/SQRT(10)</f>
+      <c r="C15" s="34">
+        <f>C14/SQRT(10)</f>
         <v>2.3888630489558158e-004</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="6">
-        <f>E13/SQRT(10)</f>
+      <c r="D15" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="33">
+        <f>E14/SQRT(10)</f>
         <v>1.1127343698195788e-003</v>
       </c>
-      <c r="F14" s="6">
-        <f>F13/SQRT(10)</f>
+      <c r="F15" s="36">
+        <f>F14/SQRT(10)</f>
         <v>9.3171884171138343e-004</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H14" s="6">
-        <f>H13/SQRT(10)</f>
-        <v>1.3119112436104082e-004</v>
-      </c>
-      <c r="I14" s="6">
-        <f>I13/SQRT(10)</f>
-        <v>3.679371927079062e-004</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
@@ -1780,311 +1766,291 @@
   <sheetData>
     <row r="1">
       <c r="A1"/>
-      <c r="B1" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>4</v>
-      </c>
+      <c r="B1" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2">
       <c r="A2"/>
-      <c r="B2" s="33">
+      <c r="B2" s="40">
         <v>0.14999999999999999</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="41">
         <v>0.20000000000000001</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="42">
         <v>0.25</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="43">
         <v>0.29999999999999999</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="42">
         <v>0.34999999999999998</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="44">
         <v>0.40000000000000002</v>
       </c>
-      <c r="H2" s="33">
+      <c r="H2" s="40">
         <v>0.45000000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3"/>
-      <c r="B3" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>8</v>
-      </c>
+      <c r="B3" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" s="38">
+      <c r="B4" s="48">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="49">
         <v>0.16980000000000001</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="50">
         <v>0.19339999999999999</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="50">
         <v>0.21460000000000001</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="50">
         <v>0.23419999999999999</v>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="51">
         <v>0.25280000000000002</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="48">
         <v>0.27129999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5"/>
-      <c r="B5" s="42">
+      <c r="B5" s="52">
         <v>0.1434</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="53">
         <v>0.1716</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="54">
         <v>0.19320000000000001</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="54">
         <v>0.215</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="54">
         <v>0.2344</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="55">
         <v>0.253</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="52">
         <v>0.27189999999999998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6"/>
-      <c r="B6" s="42">
+      <c r="B6" s="52">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="53">
         <v>0.17100000000000001</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="54">
         <v>0.1933</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="54">
         <v>0.21490000000000001</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="54">
         <v>0.23430000000000001</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="55">
         <v>0.25369999999999998</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="52">
         <v>0.27210000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7"/>
-      <c r="B7" s="42">
+      <c r="B7" s="52">
         <v>0.1431</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="53">
         <v>0.17030000000000001</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="54">
         <v>0.1933</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="54">
         <v>0.21479999999999999</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="54">
         <v>0.23419999999999999</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="55">
         <v>0.25319999999999998</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="52">
         <v>0.27079999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8"/>
-      <c r="B8" s="42">
+      <c r="B8" s="52">
         <v>0.14319999999999999</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="53">
         <v>0.1706</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="54">
         <v>0.1933</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="54">
         <v>0.2152</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="54">
         <v>0.2344</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="55">
         <v>0.25359999999999999</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="52">
         <v>0.27179999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9"/>
-      <c r="B9" s="42">
+      <c r="B9" s="52">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="53">
         <v>0.1711</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="54">
         <v>0.19359999999999999</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="54">
         <v>0.2147</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="54">
         <v>0.23449999999999999</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="55">
         <v>0.253</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="52">
         <v>0.26860000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10"/>
-      <c r="B10" s="43">
+      <c r="B10" s="56">
         <v>0.1431</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="53">
         <v>0.17000000000000001</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="54">
         <v>0.19359999999999999</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="54">
         <v>0.21479999999999999</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="54">
         <v>0.23430000000000001</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="55">
         <v>0.25340000000000001</v>
       </c>
-      <c r="H10" s="43">
+      <c r="H10" s="56">
         <v>0.26829999999999998</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="45">
+      <c r="A11" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="57">
         <f t="shared" ref="B11:H11" si="0">AVERAGE(B4:B10)</f>
         <v>0.14324285714285714</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="58">
         <f t="shared" si="0"/>
         <v>0.17062857142857141</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="58">
         <f t="shared" si="0"/>
         <v>0.19338571428571427</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="58">
         <f t="shared" si="0"/>
         <v>0.21485714285714286</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="58">
         <f t="shared" si="0"/>
         <v>0.23432857142857141</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="59">
         <f t="shared" si="0"/>
         <v>0.25324285714285721</v>
       </c>
-      <c r="H11" s="48">
+      <c r="H11" s="60">
         <f t="shared" si="0"/>
         <v>0.27068571428571425</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="50">
+      <c r="A12" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="62">
         <f t="shared" ref="B12:H12" si="1">_xlfn.STDEV.S(B4:B10)/SQRT(7)</f>
         <v>4.2857142857143202e-005</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="63">
         <f t="shared" si="1"/>
         <v>2.4369603013188476e-004</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="63">
         <f t="shared" si="1"/>
         <v>5.9476171413316292e-005</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="63">
         <f t="shared" si="1"/>
         <v>7.514158970504462e-005</v>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="63">
         <f t="shared" si="1"/>
         <v>4.2056004125370102e-005</v>
       </c>
-      <c r="G12" s="52">
+      <c r="G12" s="64">
         <f t="shared" si="1"/>
         <v>1.2697420596164739e-004</v>
       </c>
-      <c r="H12" s="53">
+      <c r="H12" s="65">
         <f t="shared" si="1"/>
         <v>6.0056662586997192e-004</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:H3"/>
+  </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/Kater.xlsx
+++ b/Kater.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Periodi" sheetId="1" state="visible" r:id="rId1"/>
@@ -41,13 +41,13 @@
     <t xml:space="preserve">0,920 m</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>M</t>
   </si>
   <si>
-    <t xml:space="preserve">Deviazione standard</t>
+    <t>σ</t>
   </si>
   <si>
-    <t xml:space="preserve">Err. media</t>
+    <t>σM</t>
   </si>
   <si>
     <t xml:space="preserve">Distanza [m]</t>
@@ -56,16 +56,17 @@
     <t xml:space="preserve">Tempi [s]</t>
   </si>
   <si>
-    <t xml:space="preserve">Errore della media</t>
+    <t xml:space="preserve">σm </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.00000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -84,14 +85,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.249977111117893"/>
-        <bgColor theme="3" tint="0.249977111117893"/>
+        <fgColor rgb="FF4285F4"/>
+        <bgColor rgb="FF4285F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
-        <bgColor theme="3" tint="0.499984740745262"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -541,22 +542,23 @@
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="8" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -568,25 +570,25 @@
     <xf fontId="0" fillId="2" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="9" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="12" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="0" fillId="2" borderId="4" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="13" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="17" numFmtId="164" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -610,24 +612,23 @@
     <xf fontId="0" fillId="2" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="33" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="34" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="35" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="4" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="36" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="37" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="38" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="5" numFmtId="165" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="4" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="33" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="34" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="35" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="36" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="37" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="38" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="5" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1445,18 +1446,18 @@
       <c r="C26">
         <v>1.9802999999999999</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="8">
         <v>1.9879</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="8">
+      <c r="B27" s="9">
         <v>0.92000000000000004</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="10">
         <v>1.9931000000000001</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="11">
         <v>1.9933000000000001</v>
       </c>
     </row>
@@ -1472,10 +1473,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="22.86328125"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="16.203125"/>
     <col customWidth="1" min="2" max="2" width="18.00390625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="18.796875"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="22.86328125"/>
+    <col customWidth="1" min="4" max="4" width="16.375"/>
     <col customWidth="1" min="5" max="5" width="17.625"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="18.796875"/>
     <col bestFit="1" min="7" max="7" width="22.86328125"/>
@@ -1488,45 +1489,45 @@
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="E1" s="13" t="s">
+      <c r="C1" s="13"/>
+      <c r="E1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="14"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="18">
+      <c r="B3" s="19">
         <v>1.9906999999999999</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="19">
         <v>1.9875</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="19">
         <v>1.9911000000000001</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="20">
         <v>1.9866999999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="5">
+      <c r="B4" s="8">
         <v>1.9911000000000001</v>
       </c>
       <c r="C4" s="7">
@@ -1536,13 +1537,13 @@
       <c r="E4" s="7">
         <v>1.9863</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <v>1.9923999999999999</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21"/>
-      <c r="B5" s="5">
+      <c r="A5" s="22"/>
+      <c r="B5" s="8">
         <v>1.9908999999999999</v>
       </c>
       <c r="C5" s="7">
@@ -1552,13 +1553,13 @@
       <c r="E5" s="7">
         <v>1.9910000000000001</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="21">
         <v>1.9919</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21"/>
-      <c r="B6" s="5">
+      <c r="A6" s="22"/>
+      <c r="B6" s="8">
         <v>1.9919</v>
       </c>
       <c r="C6" s="7">
@@ -1568,13 +1569,13 @@
       <c r="E6" s="7">
         <v>1.9857</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>1.9925999999999999</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21"/>
-      <c r="B7" s="5">
+      <c r="A7" s="22"/>
+      <c r="B7" s="8">
         <v>1.9908999999999999</v>
       </c>
       <c r="C7" s="7">
@@ -1584,13 +1585,13 @@
       <c r="E7" s="7">
         <v>1.9905999999999999</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>1.9903999999999999</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21"/>
-      <c r="B8" s="5">
+      <c r="A8" s="22"/>
+      <c r="B8" s="8">
         <v>1.9906999999999999</v>
       </c>
       <c r="C8" s="7">
@@ -1600,13 +1601,13 @@
       <c r="E8" s="7">
         <v>1.9925999999999999</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <v>1.9904999999999999</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21"/>
-      <c r="B9" s="5">
+      <c r="A9" s="22"/>
+      <c r="B9" s="8">
         <v>1.9913000000000001</v>
       </c>
       <c r="C9" s="7">
@@ -1616,13 +1617,13 @@
       <c r="E9" s="7">
         <v>1.9928999999999999</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <v>1.9907999999999999</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21"/>
-      <c r="B10" s="5">
+      <c r="A10" s="22"/>
+      <c r="B10" s="8">
         <v>1.9904999999999999</v>
       </c>
       <c r="C10" s="7">
@@ -1632,13 +1633,13 @@
       <c r="E10" s="7">
         <v>1.9905999999999999</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <v>1.9937</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21"/>
-      <c r="B11" s="5">
+      <c r="A11" s="22"/>
+      <c r="B11" s="8">
         <v>1.9905999999999999</v>
       </c>
       <c r="C11" s="7">
@@ -1648,93 +1649,93 @@
       <c r="E11" s="7">
         <v>1.982</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <v>1.99</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21"/>
-      <c r="B12" s="5">
+      <c r="A12" s="22"/>
+      <c r="B12" s="8">
         <v>1.9923</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="11">
         <v>1.9870000000000001</v>
       </c>
       <c r="E12" s="7">
         <v>1.9910000000000001</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <v>1.9839</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="24">
         <f>AVERAGE(B3:B12)</f>
         <v>1.9910900000000002</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <f>AVERAGE(C3:C12)</f>
         <v>1.9881199999999999</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="24">
         <f>AVERAGE(E3:E12)</f>
         <v>1.9893800000000001</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>AVERAGE(F3:F12)</f>
         <v>1.9902899999999994</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="29">
         <f>_xlfn.STDEV.S(B3:B12)</f>
         <v>5.8963265400306707e-004</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>_xlfn.STDEV.S(C3:C12)</f>
         <v>7.554248252914698e-004</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="29">
         <f>_xlfn.STDEV.S(E3:E12)</f>
         <v>3.5187750393819938e-003</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>_xlfn.STDEV.S(F3:F12)</f>
         <v>2.9463536787018665e-003</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="34">
         <f>B14/SQRT(10)</f>
         <v>1.8645821694596905e-004</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>C14/SQRT(10)</f>
         <v>2.3888630489558158e-004</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>E14/SQRT(10)</f>
         <v>1.1127343698195788e-003</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="37">
         <f>F14/SQRT(10)</f>
         <v>9.3171884171138343e-004</v>
       </c>
@@ -1766,255 +1767,255 @@
   <sheetData>
     <row r="1">
       <c r="A1"/>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2">
       <c r="A2"/>
-      <c r="B2" s="40">
+      <c r="B2" s="41">
         <v>0.14999999999999999</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="42">
         <v>0.20000000000000001</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="43">
         <v>0.25</v>
       </c>
-      <c r="E2" s="43">
+      <c r="E2" s="44">
         <v>0.29999999999999999</v>
       </c>
-      <c r="F2" s="42">
+      <c r="F2" s="43">
         <v>0.34999999999999998</v>
       </c>
-      <c r="G2" s="44">
+      <c r="G2" s="45">
         <v>0.40000000000000002</v>
       </c>
-      <c r="H2" s="40">
+      <c r="H2" s="41">
         <v>0.45000000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3"/>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="48"/>
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" s="48">
+      <c r="B4" s="49">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C4" s="49">
+      <c r="C4" s="50">
         <v>0.16980000000000001</v>
       </c>
-      <c r="D4" s="50">
+      <c r="D4" s="51">
         <v>0.19339999999999999</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="51">
         <v>0.21460000000000001</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="51">
         <v>0.23419999999999999</v>
       </c>
-      <c r="G4" s="51">
+      <c r="G4" s="52">
         <v>0.25280000000000002</v>
       </c>
-      <c r="H4" s="48">
+      <c r="H4" s="49">
         <v>0.27129999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5"/>
-      <c r="B5" s="52">
+      <c r="B5" s="53">
         <v>0.1434</v>
       </c>
-      <c r="C5" s="53">
+      <c r="C5" s="54">
         <v>0.1716</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="55">
         <v>0.19320000000000001</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="55">
         <v>0.215</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="55">
         <v>0.2344</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="56">
         <v>0.253</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5" s="53">
         <v>0.27189999999999998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6"/>
-      <c r="B6" s="52">
+      <c r="B6" s="53">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C6" s="53">
+      <c r="C6" s="54">
         <v>0.17100000000000001</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="55">
         <v>0.1933</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="55">
         <v>0.21490000000000001</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="55">
         <v>0.23430000000000001</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="56">
         <v>0.25369999999999998</v>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="53">
         <v>0.27210000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7"/>
-      <c r="B7" s="52">
+      <c r="B7" s="53">
         <v>0.1431</v>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="54">
         <v>0.17030000000000001</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="55">
         <v>0.1933</v>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="55">
         <v>0.21479999999999999</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="55">
         <v>0.23419999999999999</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="56">
         <v>0.25319999999999998</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="53">
         <v>0.27079999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8"/>
-      <c r="B8" s="52">
+      <c r="B8" s="53">
         <v>0.14319999999999999</v>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="54">
         <v>0.1706</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="55">
         <v>0.1933</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="55">
         <v>0.2152</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="55">
         <v>0.2344</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="56">
         <v>0.25359999999999999</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="53">
         <v>0.27179999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9"/>
-      <c r="B9" s="52">
+      <c r="B9" s="53">
         <v>0.14330000000000001</v>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="54">
         <v>0.1711</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="55">
         <v>0.19359999999999999</v>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="55">
         <v>0.2147</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="55">
         <v>0.23449999999999999</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="56">
         <v>0.253</v>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="53">
         <v>0.26860000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10"/>
-      <c r="B10" s="56">
+      <c r="B10" s="57">
         <v>0.1431</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="54">
         <v>0.17000000000000001</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="55">
         <v>0.19359999999999999</v>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="55">
         <v>0.21479999999999999</v>
       </c>
-      <c r="F10" s="54">
+      <c r="F10" s="55">
         <v>0.23430000000000001</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="56">
         <v>0.25340000000000001</v>
       </c>
-      <c r="H10" s="56">
+      <c r="H10" s="57">
         <v>0.26829999999999998</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="57">
+      <c r="B11" s="58">
         <f t="shared" ref="B11:H11" si="0">AVERAGE(B4:B10)</f>
         <v>0.14324285714285714</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="59">
         <f t="shared" si="0"/>
         <v>0.17062857142857141</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="59">
         <f t="shared" si="0"/>
         <v>0.19338571428571427</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="59">
         <f t="shared" si="0"/>
         <v>0.21485714285714286</v>
       </c>
-      <c r="F11" s="58">
+      <c r="F11" s="59">
         <f t="shared" si="0"/>
         <v>0.23432857142857141</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="60">
         <f t="shared" si="0"/>
         <v>0.25324285714285721</v>
       </c>
-      <c r="H11" s="60">
+      <c r="H11" s="61">
         <f t="shared" si="0"/>
         <v>0.27068571428571425</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="33" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="62">
